--- a/research/traditional_assets/database/data/turkey/turkey_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_heathcare_information_and_technology.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1672025832930891</v>
+        <v>0.1668183268348564</v>
       </c>
       <c r="C2">
-        <v>68.9548865707193</v>
+        <v>68.48375276102681</v>
       </c>
       <c r="D2">
-        <v>68.77888657071929</v>
+        <v>68.99727276102681</v>
       </c>
       <c r="E2">
-        <v>-0.552</v>
+        <v>0.1375200000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6895200000000001</v>
       </c>
       <c r="G2">
         <v>0.176</v>
@@ -1451,28 +1451,28 @@
         <v>2.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.034682856</v>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.065317144</v>
       </c>
       <c r="O2">
-        <v>0.525</v>
+        <v>0.5163292860000001</v>
       </c>
       <c r="P2">
-        <v>1.575</v>
+        <v>1.548987858</v>
       </c>
       <c r="Q2">
-        <v>1.105</v>
+        <v>1.078987858</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1672025832930891</v>
+        <v>0.1681222998331882</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.182950128167228</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>60.54864685883999</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1668183268348564</v>
+        <v>0.1664340703766236</v>
       </c>
       <c r="C3">
-        <v>68.48375276102681</v>
+        <v>68.01401020512778</v>
       </c>
       <c r="D3">
-        <v>68.99727276102681</v>
+        <v>69.21705020512778</v>
       </c>
       <c r="E3">
-        <v>0.1375200000000001</v>
+        <v>0.8270400000000002</v>
       </c>
       <c r="F3">
-        <v>0.6895200000000001</v>
+        <v>1.37904</v>
       </c>
       <c r="G3">
         <v>0.176</v>
@@ -1533,28 +1533,28 @@
         <v>2.1</v>
       </c>
       <c r="M3">
-        <v>0.034682856</v>
+        <v>0.06936571200000001</v>
       </c>
       <c r="N3">
-        <v>2.065317144</v>
+        <v>2.030634288</v>
       </c>
       <c r="O3">
-        <v>0.5163292860000001</v>
+        <v>0.507658572</v>
       </c>
       <c r="P3">
-        <v>1.548987858</v>
+        <v>1.522975716</v>
       </c>
       <c r="Q3">
-        <v>1.078987858</v>
+        <v>1.052975716</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1681222998331882</v>
+        <v>0.1690607860985955</v>
       </c>
       <c r="T3">
-        <v>1.182950128167228</v>
+        <v>1.192026007622248</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>60.54864685883999</v>
+        <v>30.27432342941999</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1664340703766236</v>
+        <v>0.1660498139183909</v>
       </c>
       <c r="C4">
-        <v>68.01401020512778</v>
+        <v>67.54567224021342</v>
       </c>
       <c r="D4">
-        <v>69.21705020512778</v>
+        <v>69.43823224021342</v>
       </c>
       <c r="E4">
-        <v>0.8270400000000002</v>
+        <v>1.51656</v>
       </c>
       <c r="F4">
-        <v>1.37904</v>
+        <v>2.06856</v>
       </c>
       <c r="G4">
         <v>0.176</v>
@@ -1615,28 +1615,28 @@
         <v>2.1</v>
       </c>
       <c r="M4">
-        <v>0.06936571200000001</v>
+        <v>0.104048568</v>
       </c>
       <c r="N4">
-        <v>2.030634288</v>
+        <v>1.995951432</v>
       </c>
       <c r="O4">
-        <v>0.507658572</v>
+        <v>0.498987858</v>
       </c>
       <c r="P4">
-        <v>1.522975716</v>
+        <v>1.496963574</v>
       </c>
       <c r="Q4">
-        <v>1.052975716</v>
+        <v>1.026963574</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1690607860985955</v>
+        <v>0.1700186225962793</v>
       </c>
       <c r="T4">
-        <v>1.192026007622248</v>
+        <v>1.201289018612422</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.27432342941999</v>
+        <v>20.18288228628</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1660498139183909</v>
+        <v>0.1656655574601582</v>
       </c>
       <c r="C5">
-        <v>67.54567224021342</v>
+        <v>67.07875237449664</v>
       </c>
       <c r="D5">
-        <v>69.43823224021342</v>
+        <v>69.66083237449665</v>
       </c>
       <c r="E5">
-        <v>1.51656</v>
+        <v>2.20608</v>
       </c>
       <c r="F5">
-        <v>2.06856</v>
+        <v>2.758080000000001</v>
       </c>
       <c r="G5">
         <v>0.176</v>
@@ -1697,28 +1697,28 @@
         <v>2.1</v>
       </c>
       <c r="M5">
-        <v>0.104048568</v>
+        <v>0.138731424</v>
       </c>
       <c r="N5">
-        <v>1.995951432</v>
+        <v>1.961268576</v>
       </c>
       <c r="O5">
-        <v>0.498987858</v>
+        <v>0.490317144</v>
       </c>
       <c r="P5">
-        <v>1.496963574</v>
+        <v>1.470951432</v>
       </c>
       <c r="Q5">
-        <v>1.026963574</v>
+        <v>1.000951432</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1700186225962793</v>
+        <v>0.1709964140209981</v>
       </c>
       <c r="T5">
-        <v>1.201289018612422</v>
+        <v>1.210745008998225</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.18288228628</v>
+        <v>15.13716171471</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1656655574601582</v>
+        <v>0.1653375510019255</v>
       </c>
       <c r="C6">
-        <v>67.07875237449664</v>
+        <v>66.58037902852449</v>
       </c>
       <c r="D6">
-        <v>69.66083237449665</v>
+        <v>69.85197902852448</v>
       </c>
       <c r="E6">
-        <v>2.20608</v>
+        <v>2.895600000000001</v>
       </c>
       <c r="F6">
-        <v>2.758080000000001</v>
+        <v>3.447600000000001</v>
       </c>
       <c r="G6">
         <v>0.176</v>
@@ -1779,45 +1779,45 @@
         <v>2.1</v>
       </c>
       <c r="M6">
-        <v>0.138731424</v>
+        <v>0.1785856800000001</v>
       </c>
       <c r="N6">
-        <v>1.961268576</v>
+        <v>1.92141432</v>
       </c>
       <c r="O6">
-        <v>0.490317144</v>
+        <v>0.48035358</v>
       </c>
       <c r="P6">
-        <v>1.470951432</v>
+        <v>1.44106074</v>
       </c>
       <c r="Q6">
-        <v>1.000951432</v>
+        <v>0.9710607399999998</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1709964140209981</v>
+        <v>0.1719947905283426</v>
       </c>
       <c r="T6">
-        <v>1.210745008998225</v>
+        <v>1.220400072865835</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.13716171471</v>
+        <v>11.75906153281719</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1653375510019255</v>
+        <v>0.1650410445436928</v>
       </c>
       <c r="C7">
-        <v>66.58037902852449</v>
+        <v>66.06455394189557</v>
       </c>
       <c r="D7">
-        <v>69.85197902852448</v>
+        <v>70.02567394189556</v>
       </c>
       <c r="E7">
-        <v>2.895600000000001</v>
+        <v>3.585120000000001</v>
       </c>
       <c r="F7">
-        <v>3.447600000000001</v>
+        <v>4.137120000000001</v>
       </c>
       <c r="G7">
         <v>0.176</v>
@@ -1861,45 +1861,45 @@
         <v>2.1</v>
       </c>
       <c r="M7">
-        <v>0.1785856800000001</v>
+        <v>0.2213359200000001</v>
       </c>
       <c r="N7">
-        <v>1.92141432</v>
+        <v>1.87866408</v>
       </c>
       <c r="O7">
-        <v>0.48035358</v>
+        <v>0.46966602</v>
       </c>
       <c r="P7">
-        <v>1.44106074</v>
+        <v>1.40899806</v>
       </c>
       <c r="Q7">
-        <v>0.9710607399999998</v>
+        <v>0.9389980599999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1719947905283426</v>
+        <v>0.1730144090890348</v>
       </c>
       <c r="T7">
-        <v>1.220400072865835</v>
+        <v>1.230260563624244</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>11.75906153281719</v>
+        <v>9.487840925232558</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1650410445436928</v>
+        <v>0.16468078808546</v>
       </c>
       <c r="C8">
-        <v>66.06455394189557</v>
+        <v>65.58723981372688</v>
       </c>
       <c r="D8">
-        <v>70.02567394189556</v>
+        <v>70.23787981372688</v>
       </c>
       <c r="E8">
-        <v>3.58512</v>
+        <v>4.27464</v>
       </c>
       <c r="F8">
-        <v>4.13712</v>
+        <v>4.82664</v>
       </c>
       <c r="G8">
         <v>0.176</v>
@@ -1943,28 +1943,28 @@
         <v>2.1</v>
       </c>
       <c r="M8">
-        <v>0.22133592</v>
+        <v>0.25822524</v>
       </c>
       <c r="N8">
-        <v>1.87866408</v>
+        <v>1.84177476</v>
       </c>
       <c r="O8">
-        <v>0.46966602</v>
+        <v>0.46044369</v>
       </c>
       <c r="P8">
-        <v>1.40899806</v>
+        <v>1.38133107</v>
       </c>
       <c r="Q8">
-        <v>0.9389980599999999</v>
+        <v>0.9113310699999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1730144090890348</v>
+        <v>0.1740559549306022</v>
       </c>
       <c r="T8">
-        <v>1.230260563624244</v>
+        <v>1.240333107947351</v>
       </c>
       <c r="U8">
         <v>0.0535</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>9.487840925232559</v>
+        <v>8.132435078770765</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.16468078808546</v>
+        <v>0.1643685316272273</v>
       </c>
       <c r="C9">
-        <v>65.5872398137269</v>
+        <v>65.082694960871</v>
       </c>
       <c r="D9">
-        <v>70.23787981372689</v>
+        <v>70.42285496087099</v>
       </c>
       <c r="E9">
-        <v>4.274640000000002</v>
+        <v>4.964160000000001</v>
       </c>
       <c r="F9">
-        <v>4.826640000000001</v>
+        <v>5.516160000000001</v>
       </c>
       <c r="G9">
         <v>0.176</v>
@@ -2025,45 +2025,45 @@
         <v>2.1</v>
       </c>
       <c r="M9">
-        <v>0.2582252400000001</v>
+        <v>0.2995274880000001</v>
       </c>
       <c r="N9">
-        <v>1.84177476</v>
+        <v>1.800472512</v>
       </c>
       <c r="O9">
-        <v>0.46044369</v>
+        <v>0.450118128</v>
       </c>
       <c r="P9">
-        <v>1.38133107</v>
+        <v>1.350354384</v>
       </c>
       <c r="Q9">
-        <v>0.9113310699999999</v>
+        <v>0.8803543839999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1740559549306022</v>
+        <v>0.1751201430730732</v>
       </c>
       <c r="T9">
-        <v>1.240333107947351</v>
+        <v>1.250624620625308</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.132435078770765</v>
+        <v>7.011042672651131</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1643685316272273</v>
+        <v>0.1640142751689946</v>
       </c>
       <c r="C10">
-        <v>65.082694960871</v>
+        <v>64.60421335823385</v>
       </c>
       <c r="D10">
-        <v>70.42285496087099</v>
+        <v>70.63389335823385</v>
       </c>
       <c r="E10">
-        <v>4.964160000000001</v>
+        <v>5.653680000000001</v>
       </c>
       <c r="F10">
-        <v>5.516160000000001</v>
+        <v>6.205680000000001</v>
       </c>
       <c r="G10">
         <v>0.176</v>
@@ -2107,28 +2107,28 @@
         <v>2.1</v>
       </c>
       <c r="M10">
-        <v>0.2995274880000001</v>
+        <v>0.336968424</v>
       </c>
       <c r="N10">
-        <v>1.800472512</v>
+        <v>1.763031576</v>
       </c>
       <c r="O10">
-        <v>0.450118128</v>
+        <v>0.440757894</v>
       </c>
       <c r="P10">
-        <v>1.350354384</v>
+        <v>1.322273682</v>
       </c>
       <c r="Q10">
-        <v>0.8803543839999999</v>
+        <v>0.8522736819999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1751201430730732</v>
+        <v>0.1762077199659281</v>
       </c>
       <c r="T10">
-        <v>1.250624620625308</v>
+        <v>1.261142320395088</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.011042672651131</v>
+        <v>6.232037931245451</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1640142751689946</v>
+        <v>0.1637350187107618</v>
       </c>
       <c r="C11">
-        <v>64.60421335823385</v>
+        <v>64.08194623279169</v>
       </c>
       <c r="D11">
-        <v>70.63389335823385</v>
+        <v>70.80114623279169</v>
       </c>
       <c r="E11">
-        <v>5.653680000000001</v>
+        <v>6.343200000000001</v>
       </c>
       <c r="F11">
-        <v>6.205680000000001</v>
+        <v>6.895200000000001</v>
       </c>
       <c r="G11">
         <v>0.176</v>
@@ -2189,45 +2189,45 @@
         <v>2.1</v>
       </c>
       <c r="M11">
-        <v>0.336968424</v>
+        <v>0.3813045600000001</v>
       </c>
       <c r="N11">
-        <v>1.763031576</v>
+        <v>1.71869544</v>
       </c>
       <c r="O11">
-        <v>0.440757894</v>
+        <v>0.42967386</v>
       </c>
       <c r="P11">
-        <v>1.322273682</v>
+        <v>1.28902158</v>
       </c>
       <c r="Q11">
-        <v>0.8522736819999999</v>
+        <v>0.8190215799999998</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1762077199659281</v>
+        <v>0.1773194652341798</v>
       </c>
       <c r="T11">
-        <v>1.261142320395088</v>
+        <v>1.271893746826418</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.232037931245451</v>
+        <v>5.507408566002987</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1637350187107618</v>
+        <v>0.1633882622525291</v>
       </c>
       <c r="C12">
-        <v>64.08194623279169</v>
+        <v>63.60121199283444</v>
       </c>
       <c r="D12">
-        <v>70.80114623279169</v>
+        <v>71.00993199283444</v>
       </c>
       <c r="E12">
-        <v>6.343200000000001</v>
+        <v>7.032720000000001</v>
       </c>
       <c r="F12">
-        <v>6.895200000000002</v>
+        <v>7.584720000000002</v>
       </c>
       <c r="G12">
         <v>0.176</v>
@@ -2271,28 +2271,28 @@
         <v>2.1</v>
       </c>
       <c r="M12">
-        <v>0.3813045600000001</v>
+        <v>0.4194350160000001</v>
       </c>
       <c r="N12">
-        <v>1.71869544</v>
+        <v>1.680564984</v>
       </c>
       <c r="O12">
-        <v>0.42967386</v>
+        <v>0.420141246</v>
       </c>
       <c r="P12">
-        <v>1.28902158</v>
+        <v>1.260423738</v>
       </c>
       <c r="Q12">
-        <v>0.8190215799999998</v>
+        <v>0.7904237379999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1773194652341798</v>
+        <v>0.1784561935421676</v>
       </c>
       <c r="T12">
-        <v>1.271893746826418</v>
+        <v>1.282886778346094</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.507408566002986</v>
+        <v>5.006735060002715</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1633882622525291</v>
+        <v>0.1630415057942964</v>
       </c>
       <c r="C13">
-        <v>63.60121199283444</v>
+        <v>63.12171277302112</v>
       </c>
       <c r="D13">
-        <v>71.00993199283444</v>
+        <v>71.21995277302112</v>
       </c>
       <c r="E13">
-        <v>7.032720000000001</v>
+        <v>7.722240000000001</v>
       </c>
       <c r="F13">
-        <v>7.584720000000002</v>
+        <v>8.274240000000001</v>
       </c>
       <c r="G13">
         <v>0.176</v>
@@ -2353,28 +2353,28 @@
         <v>2.1</v>
       </c>
       <c r="M13">
-        <v>0.4194350160000001</v>
+        <v>0.457565472</v>
       </c>
       <c r="N13">
-        <v>1.680564984</v>
+        <v>1.642434528</v>
       </c>
       <c r="O13">
-        <v>0.420141246</v>
+        <v>0.410608632</v>
       </c>
       <c r="P13">
-        <v>1.260423738</v>
+        <v>1.231825896</v>
       </c>
       <c r="Q13">
-        <v>0.7904237379999999</v>
+        <v>0.7618258959999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1784561935421676</v>
+        <v>0.1796187565844277</v>
       </c>
       <c r="T13">
-        <v>1.282886778346094</v>
+        <v>1.294129651491216</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.006735060002715</v>
+        <v>4.589507138335822</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1630415057942964</v>
+        <v>0.1629384993360637</v>
       </c>
       <c r="C14">
-        <v>63.12171277302112</v>
+        <v>62.4948204755462</v>
       </c>
       <c r="D14">
-        <v>71.21995277302112</v>
+        <v>71.2825804755462</v>
       </c>
       <c r="E14">
-        <v>7.722240000000001</v>
+        <v>8.411760000000003</v>
       </c>
       <c r="F14">
-        <v>8.274240000000001</v>
+        <v>8.963760000000002</v>
       </c>
       <c r="G14">
         <v>0.176</v>
@@ -2435,45 +2435,45 @@
         <v>2.1</v>
       </c>
       <c r="M14">
-        <v>0.457565472</v>
+        <v>0.5181053280000002</v>
       </c>
       <c r="N14">
-        <v>1.642434528</v>
+        <v>1.581894672</v>
       </c>
       <c r="O14">
-        <v>0.410608632</v>
+        <v>0.3954736679999999</v>
       </c>
       <c r="P14">
-        <v>1.231825896</v>
+        <v>1.186421004</v>
       </c>
       <c r="Q14">
-        <v>0.7618258959999999</v>
+        <v>0.7164210039999996</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1796187565844277</v>
+        <v>0.1808080452138663</v>
       </c>
       <c r="T14">
-        <v>1.294129651491216</v>
+        <v>1.305630981490249</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.589507138335822</v>
+        <v>4.053229886877363</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1629384993360637</v>
+        <v>0.162977992877831</v>
       </c>
       <c r="C15">
-        <v>62.4948204755462</v>
+        <v>61.78127547306789</v>
       </c>
       <c r="D15">
-        <v>71.2825804755462</v>
+        <v>71.25855547306789</v>
       </c>
       <c r="E15">
-        <v>8.411760000000003</v>
+        <v>9.101280000000003</v>
       </c>
       <c r="F15">
-        <v>8.963760000000002</v>
+        <v>9.653280000000002</v>
       </c>
       <c r="G15">
         <v>0.176</v>
@@ -2517,45 +2517,45 @@
         <v>2.1</v>
       </c>
       <c r="M15">
-        <v>0.5181053280000002</v>
+        <v>0.5917460640000002</v>
       </c>
       <c r="N15">
-        <v>1.581894672</v>
+        <v>1.508253936</v>
       </c>
       <c r="O15">
-        <v>0.3954736679999999</v>
+        <v>0.377063484</v>
       </c>
       <c r="P15">
-        <v>1.186421004</v>
+        <v>1.131190452</v>
       </c>
       <c r="Q15">
-        <v>0.7164210039999996</v>
+        <v>0.6611904519999998</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1808080452138663</v>
+        <v>0.1820249917184081</v>
       </c>
       <c r="T15">
-        <v>1.305630981490249</v>
+        <v>1.317399784279957</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.053229886877363</v>
+        <v>3.548819549055758</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.162977992877831</v>
+        <v>0.1629912364195983</v>
       </c>
       <c r="C16">
-        <v>61.78127547306789</v>
+        <v>61.08370268956194</v>
       </c>
       <c r="D16">
-        <v>71.25855547306789</v>
+        <v>71.25050268956194</v>
       </c>
       <c r="E16">
-        <v>9.101280000000003</v>
+        <v>9.790800000000004</v>
       </c>
       <c r="F16">
-        <v>9.653280000000002</v>
+        <v>10.3428</v>
       </c>
       <c r="G16">
         <v>0.176</v>
@@ -2599,45 +2599,45 @@
         <v>2.1</v>
       </c>
       <c r="M16">
-        <v>0.5917460640000002</v>
+        <v>0.6629734800000003</v>
       </c>
       <c r="N16">
-        <v>1.508253936</v>
+        <v>1.43702652</v>
       </c>
       <c r="O16">
-        <v>0.377063484</v>
+        <v>0.35925663</v>
       </c>
       <c r="P16">
-        <v>1.131190452</v>
+        <v>1.07776989</v>
       </c>
       <c r="Q16">
-        <v>0.6611904519999998</v>
+        <v>0.6077698899999997</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1820249917184081</v>
+        <v>0.1832705722583509</v>
       </c>
       <c r="T16">
-        <v>1.317399784279957</v>
+        <v>1.329445500076482</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.548819549055758</v>
+        <v>3.167547516380292</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1629912364195983</v>
+        <v>0.1636464799613655</v>
       </c>
       <c r="C17">
-        <v>61.08370268956194</v>
+        <v>59.99801954790244</v>
       </c>
       <c r="D17">
-        <v>71.25050268956194</v>
+        <v>70.85433954790244</v>
       </c>
       <c r="E17">
-        <v>9.790800000000003</v>
+        <v>10.48032</v>
       </c>
       <c r="F17">
-        <v>10.3428</v>
+        <v>11.03232</v>
       </c>
       <c r="G17">
         <v>0.176</v>
@@ -2681,45 +2681,45 @@
         <v>2.1</v>
       </c>
       <c r="M17">
-        <v>0.6629734800000002</v>
+        <v>0.7932238080000003</v>
       </c>
       <c r="N17">
-        <v>1.43702652</v>
+        <v>1.306776192</v>
       </c>
       <c r="O17">
-        <v>0.35925663</v>
+        <v>0.326694048</v>
       </c>
       <c r="P17">
-        <v>1.07776989</v>
+        <v>0.9800821439999998</v>
       </c>
       <c r="Q17">
-        <v>0.6077698899999997</v>
+        <v>0.5100821439999996</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1832705722583509</v>
+        <v>0.1845458094778161</v>
       </c>
       <c r="T17">
-        <v>1.329445500076482</v>
+        <v>1.341778018630068</v>
       </c>
       <c r="U17">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.167547516380292</v>
+        <v>2.647424319366873</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1636464799613655</v>
+        <v>0.1639214735031328</v>
       </c>
       <c r="C18">
-        <v>59.99801954790244</v>
+        <v>59.14354659562369</v>
       </c>
       <c r="D18">
-        <v>70.85433954790244</v>
+        <v>70.68938659562369</v>
       </c>
       <c r="E18">
-        <v>10.48032</v>
+        <v>11.16984</v>
       </c>
       <c r="F18">
-        <v>11.03232</v>
+        <v>11.72184</v>
       </c>
       <c r="G18">
         <v>0.176</v>
@@ -2763,45 +2763,45 @@
         <v>2.1</v>
       </c>
       <c r="M18">
-        <v>0.7932238080000003</v>
+        <v>0.8885154720000004</v>
       </c>
       <c r="N18">
-        <v>1.306776192</v>
+        <v>1.211484528</v>
       </c>
       <c r="O18">
-        <v>0.326694048</v>
+        <v>0.3028711319999999</v>
       </c>
       <c r="P18">
-        <v>0.9800821439999998</v>
+        <v>0.9086133959999998</v>
       </c>
       <c r="Q18">
-        <v>0.5100821439999996</v>
+        <v>0.4386133959999996</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1845458094778161</v>
+        <v>0.1858517753049793</v>
       </c>
       <c r="T18">
-        <v>1.341778018630068</v>
+        <v>1.354407706305426</v>
       </c>
       <c r="U18">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.647424319366873</v>
+        <v>2.363492889181787</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1639214735031328</v>
+        <v>0.1637284670449001</v>
       </c>
       <c r="C19">
-        <v>59.14354659562369</v>
+        <v>58.56971968045173</v>
       </c>
       <c r="D19">
-        <v>70.68938659562369</v>
+        <v>70.80507968045173</v>
       </c>
       <c r="E19">
-        <v>11.16984</v>
+        <v>11.85936</v>
       </c>
       <c r="F19">
-        <v>11.72184</v>
+        <v>12.41136</v>
       </c>
       <c r="G19">
         <v>0.176</v>
@@ -2845,28 +2845,28 @@
         <v>2.1</v>
       </c>
       <c r="M19">
-        <v>0.8885154720000004</v>
+        <v>0.9407810880000004</v>
       </c>
       <c r="N19">
-        <v>1.211484528</v>
+        <v>1.159218912</v>
       </c>
       <c r="O19">
-        <v>0.3028711319999999</v>
+        <v>0.2898047279999999</v>
       </c>
       <c r="P19">
-        <v>0.9086133959999998</v>
+        <v>0.8694141839999997</v>
       </c>
       <c r="Q19">
-        <v>0.4386133959999996</v>
+        <v>0.3994141839999995</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1858517753049793</v>
+        <v>0.1871895939571952</v>
       </c>
       <c r="T19">
-        <v>1.354407706305426</v>
+        <v>1.367345435143598</v>
       </c>
       <c r="U19">
         <v>0.07580000000000001</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>2.363492889181787</v>
+        <v>2.232187728671688</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1637284670449001</v>
+        <v>0.1635354605866674</v>
       </c>
       <c r="C20">
-        <v>58.56971968045171</v>
+        <v>57.99627208196875</v>
       </c>
       <c r="D20">
-        <v>70.80507968045171</v>
+        <v>70.92115208196876</v>
       </c>
       <c r="E20">
-        <v>11.85936</v>
+        <v>12.54888</v>
       </c>
       <c r="F20">
-        <v>12.41136</v>
+        <v>13.10088</v>
       </c>
       <c r="G20">
         <v>0.176</v>
@@ -2927,28 +2927,28 @@
         <v>2.1</v>
       </c>
       <c r="M20">
-        <v>0.9407810880000003</v>
+        <v>0.9930467040000002</v>
       </c>
       <c r="N20">
-        <v>1.159218912</v>
+        <v>1.106953296</v>
       </c>
       <c r="O20">
-        <v>0.289804728</v>
+        <v>0.276738324</v>
       </c>
       <c r="P20">
-        <v>0.8694141839999998</v>
+        <v>0.8302149719999999</v>
       </c>
       <c r="Q20">
-        <v>0.3994141839999996</v>
+        <v>0.3602149719999997</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1871895939571952</v>
+        <v>0.1885604451687251</v>
       </c>
       <c r="T20">
-        <v>1.367345435143598</v>
+        <v>1.38060261407654</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.232187728671688</v>
+        <v>2.114704164004757</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1635354605866674</v>
+        <v>0.1633424541284346</v>
       </c>
       <c r="C21">
-        <v>57.99627208196875</v>
+        <v>57.42320566870576</v>
       </c>
       <c r="D21">
-        <v>70.92115208196876</v>
+        <v>71.03760566870577</v>
       </c>
       <c r="E21">
-        <v>12.54888</v>
+        <v>13.2384</v>
       </c>
       <c r="F21">
-        <v>13.10088</v>
+        <v>13.7904</v>
       </c>
       <c r="G21">
         <v>0.176</v>
@@ -3009,28 +3009,28 @@
         <v>2.1</v>
       </c>
       <c r="M21">
-        <v>0.9930467040000002</v>
+        <v>1.04531232</v>
       </c>
       <c r="N21">
-        <v>1.106953296</v>
+        <v>1.05468768</v>
       </c>
       <c r="O21">
-        <v>0.276738324</v>
+        <v>0.2636719199999999</v>
       </c>
       <c r="P21">
-        <v>0.8302149719999999</v>
+        <v>0.7910157599999998</v>
       </c>
       <c r="Q21">
-        <v>0.3602149719999997</v>
+        <v>0.3210157599999997</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1885604451687251</v>
+        <v>0.1899655676605433</v>
       </c>
       <c r="T21">
-        <v>1.38060261407654</v>
+        <v>1.394191222482805</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.114704164004757</v>
+        <v>2.008968955804519</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1633424541284346</v>
+        <v>0.1653859476702019</v>
       </c>
       <c r="C22">
-        <v>57.42320566870576</v>
+        <v>55.519789795196</v>
       </c>
       <c r="D22">
-        <v>71.03760566870577</v>
+        <v>69.82370979519601</v>
       </c>
       <c r="E22">
-        <v>13.2384</v>
+        <v>13.92792</v>
       </c>
       <c r="F22">
-        <v>13.7904</v>
+        <v>14.47992</v>
       </c>
       <c r="G22">
         <v>0.176</v>
@@ -3091,45 +3091,45 @@
         <v>2.1</v>
       </c>
       <c r="M22">
-        <v>1.04531232</v>
+        <v>1.3031928</v>
       </c>
       <c r="N22">
-        <v>1.05468768</v>
+        <v>0.7968071999999997</v>
       </c>
       <c r="O22">
-        <v>0.2636719199999999</v>
+        <v>0.1992017999999999</v>
       </c>
       <c r="P22">
-        <v>0.7910157599999998</v>
+        <v>0.5976053999999997</v>
       </c>
       <c r="Q22">
-        <v>0.3210157599999997</v>
+        <v>0.1276053999999995</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1899655676605433</v>
+        <v>0.1914062628736733</v>
       </c>
       <c r="T22">
-        <v>1.394191222482805</v>
+        <v>1.40812384629176</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.008968955804519</v>
+        <v>1.611426950793466</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1653859476702019</v>
+        <v>0.1652994412119692</v>
       </c>
       <c r="C23">
-        <v>55.51978979519601</v>
+        <v>54.88081565360164</v>
       </c>
       <c r="D23">
-        <v>69.82370979519601</v>
+        <v>69.87425565360164</v>
       </c>
       <c r="E23">
-        <v>13.92792</v>
+        <v>14.61744</v>
       </c>
       <c r="F23">
-        <v>14.47992</v>
+        <v>15.16944</v>
       </c>
       <c r="G23">
         <v>0.176</v>
@@ -3173,28 +3173,28 @@
         <v>2.1</v>
       </c>
       <c r="M23">
-        <v>1.3031928</v>
+        <v>1.3652496</v>
       </c>
       <c r="N23">
-        <v>0.7968071999999999</v>
+        <v>0.7347503999999998</v>
       </c>
       <c r="O23">
-        <v>0.1992018</v>
+        <v>0.1836876</v>
       </c>
       <c r="P23">
-        <v>0.5976054</v>
+        <v>0.5510627999999999</v>
       </c>
       <c r="Q23">
-        <v>0.1276053999999998</v>
+        <v>0.08106279999999966</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1914062628736733</v>
+        <v>0.1928838989897041</v>
       </c>
       <c r="T23">
-        <v>1.40812384629176</v>
+        <v>1.422413716865047</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.611426950793466</v>
+        <v>1.538180271211945</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1652994412119692</v>
+        <v>0.1765218720163039</v>
       </c>
       <c r="C24">
-        <v>54.88081565360164</v>
+        <v>48.1926132068024</v>
       </c>
       <c r="D24">
-        <v>69.87425565360164</v>
+        <v>63.87557320680241</v>
       </c>
       <c r="E24">
-        <v>14.61744</v>
+        <v>15.30696</v>
       </c>
       <c r="F24">
-        <v>15.16944</v>
+        <v>15.85896</v>
       </c>
       <c r="G24">
         <v>0.176</v>
@@ -3255,45 +3255,45 @@
         <v>2.1</v>
       </c>
       <c r="M24">
-        <v>1.3652496</v>
+        <v>2.328095328000001</v>
       </c>
       <c r="N24">
-        <v>0.7347503999999998</v>
+        <v>-0.2280953280000007</v>
       </c>
       <c r="O24">
-        <v>0.1836876</v>
+        <v>-0.05702383200000016</v>
       </c>
       <c r="P24">
-        <v>0.5510627999999999</v>
+        <v>-0.1710714960000005</v>
       </c>
       <c r="Q24">
-        <v>0.08106279999999966</v>
+        <v>-0.6410714960000007</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1928838989897041</v>
+        <v>0.195288135530913</v>
       </c>
       <c r="T24">
-        <v>1.422413716865047</v>
+        <v>1.4456645217342</v>
       </c>
       <c r="U24">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.25</v>
+        <v>0.2255062297861369</v>
       </c>
       <c r="W24">
-        <v>0.0675</v>
+        <v>0.1136956854673951</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y24">
-        <v>1.538180271211945</v>
+        <v>0.9020249191445477</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1765218720163039</v>
+        <v>0.1775318720163039</v>
       </c>
       <c r="C25">
-        <v>48.1926132068024</v>
+        <v>47.01335349574077</v>
       </c>
       <c r="D25">
-        <v>63.87557320680241</v>
+        <v>63.38583349574077</v>
       </c>
       <c r="E25">
-        <v>15.30696</v>
+        <v>15.99648000000001</v>
       </c>
       <c r="F25">
-        <v>15.85896</v>
+        <v>16.54848</v>
       </c>
       <c r="G25">
         <v>0.176</v>
@@ -3337,37 +3337,37 @@
         <v>2.1</v>
       </c>
       <c r="M25">
-        <v>2.328095328000001</v>
+        <v>2.429316864000001</v>
       </c>
       <c r="N25">
-        <v>-0.2280953280000007</v>
+        <v>-0.3293168640000008</v>
       </c>
       <c r="O25">
-        <v>-0.05702383200000016</v>
+        <v>-0.0823292160000002</v>
       </c>
       <c r="P25">
-        <v>-0.1710714960000005</v>
+        <v>-0.2469876480000006</v>
       </c>
       <c r="Q25">
-        <v>-0.6410714960000007</v>
+        <v>-0.7169876480000008</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.195288135530913</v>
+        <v>0.1972550846826356</v>
       </c>
       <c r="T25">
-        <v>1.4456645217342</v>
+        <v>1.464686423335966</v>
       </c>
       <c r="U25">
         <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.2255062297861369</v>
+        <v>0.2161101368783812</v>
       </c>
       <c r="W25">
-        <v>0.1136956854673951</v>
+        <v>0.1150750319062536</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.9020249191445477</v>
+        <v>0.8644405475135248</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1775318720163039</v>
+        <v>0.1785418720163039</v>
       </c>
       <c r="C26">
-        <v>47.0133534957408</v>
+        <v>45.84154640080789</v>
       </c>
       <c r="D26">
-        <v>63.3858334957408</v>
+        <v>62.90354640080788</v>
       </c>
       <c r="E26">
-        <v>15.99648</v>
+        <v>16.686</v>
       </c>
       <c r="F26">
-        <v>16.54848</v>
+        <v>17.238</v>
       </c>
       <c r="G26">
         <v>0.176</v>
@@ -3419,37 +3419,37 @@
         <v>2.1</v>
       </c>
       <c r="M26">
-        <v>2.429316864</v>
+        <v>2.530538400000001</v>
       </c>
       <c r="N26">
-        <v>-0.3293168640000004</v>
+        <v>-0.4305384000000005</v>
       </c>
       <c r="O26">
-        <v>-0.08232921600000009</v>
+        <v>-0.1076346000000001</v>
       </c>
       <c r="P26">
-        <v>-0.2469876480000003</v>
+        <v>-0.3229038000000004</v>
       </c>
       <c r="Q26">
-        <v>-0.7169876480000005</v>
+        <v>-0.7929038000000006</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1972550846826356</v>
+        <v>0.1992744858117374</v>
       </c>
       <c r="T26">
-        <v>1.464686423335966</v>
+        <v>1.484215575647112</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.2161101368783813</v>
+        <v>0.207465731403246</v>
       </c>
       <c r="W26">
-        <v>0.1150750319062536</v>
+        <v>0.1163440306300035</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8644405475135251</v>
+        <v>0.829862925612984</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1785418720163039</v>
+        <v>0.1952852127655641</v>
       </c>
       <c r="C27">
-        <v>45.84154640080789</v>
+        <v>38.10640969905843</v>
       </c>
       <c r="D27">
-        <v>62.90354640080788</v>
+        <v>55.85792969905844</v>
       </c>
       <c r="E27">
-        <v>16.686</v>
+        <v>17.37552000000001</v>
       </c>
       <c r="F27">
-        <v>17.238</v>
+        <v>17.92752</v>
       </c>
       <c r="G27">
         <v>0.176</v>
@@ -3501,45 +3501,45 @@
         <v>2.1</v>
       </c>
       <c r="M27">
-        <v>2.530538400000001</v>
+        <v>3.599846016000001</v>
       </c>
       <c r="N27">
-        <v>-0.4305384000000005</v>
+        <v>-1.499846016000001</v>
       </c>
       <c r="O27">
-        <v>-0.1076346000000001</v>
+        <v>-0.3749615040000003</v>
       </c>
       <c r="P27">
-        <v>-0.3229038000000004</v>
+        <v>-1.124884512000001</v>
       </c>
       <c r="Q27">
-        <v>-0.7929038000000006</v>
+        <v>-1.594884512000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1992744858117374</v>
+        <v>0.2036367636595449</v>
       </c>
       <c r="T27">
-        <v>1.484215575647112</v>
+        <v>1.526402136447573</v>
       </c>
       <c r="U27">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.207465731403246</v>
+        <v>0.145839571377933</v>
       </c>
       <c r="W27">
-        <v>0.1163440306300035</v>
+        <v>0.1715154140673111</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.829862925612984</v>
+        <v>0.5833582855117321</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1952852127655641</v>
+        <v>0.1968352127655641</v>
       </c>
       <c r="C28">
-        <v>38.10640969905843</v>
+        <v>36.84364727798192</v>
       </c>
       <c r="D28">
-        <v>55.85792969905844</v>
+        <v>55.28468727798192</v>
       </c>
       <c r="E28">
-        <v>17.37552000000001</v>
+        <v>18.06504</v>
       </c>
       <c r="F28">
-        <v>17.92752</v>
+        <v>18.61704</v>
       </c>
       <c r="G28">
         <v>0.176</v>
@@ -3583,37 +3583,37 @@
         <v>2.1</v>
       </c>
       <c r="M28">
-        <v>3.599846016000001</v>
+        <v>3.738301632000001</v>
       </c>
       <c r="N28">
-        <v>-1.499846016000001</v>
+        <v>-1.638301632000001</v>
       </c>
       <c r="O28">
-        <v>-0.3749615040000003</v>
+        <v>-0.4095754080000001</v>
       </c>
       <c r="P28">
-        <v>-1.124884512000001</v>
+        <v>-1.228726224</v>
       </c>
       <c r="Q28">
-        <v>-1.594884512000001</v>
+        <v>-1.698726224000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2036367636595449</v>
+        <v>0.2057989111069359</v>
       </c>
       <c r="T28">
-        <v>1.526402136447573</v>
+        <v>1.547311754755074</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.145839571377933</v>
+        <v>0.1404381057713429</v>
       </c>
       <c r="W28">
-        <v>0.1715154140673111</v>
+        <v>0.1726000283611143</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.5833582855117321</v>
+        <v>0.5617524230853718</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1968352127655641</v>
+        <v>0.1983852127655641</v>
       </c>
       <c r="C29">
-        <v>36.84364727798192</v>
+        <v>35.59253114603872</v>
       </c>
       <c r="D29">
-        <v>55.28468727798192</v>
+        <v>54.72309114603872</v>
       </c>
       <c r="E29">
-        <v>18.06504</v>
+        <v>18.75456000000001</v>
       </c>
       <c r="F29">
-        <v>18.61704</v>
+        <v>19.30656</v>
       </c>
       <c r="G29">
         <v>0.176</v>
@@ -3665,37 +3665,37 @@
         <v>2.1</v>
       </c>
       <c r="M29">
-        <v>3.738301632000001</v>
+        <v>3.876757248000001</v>
       </c>
       <c r="N29">
-        <v>-1.638301632000001</v>
+        <v>-1.776757248000001</v>
       </c>
       <c r="O29">
-        <v>-0.4095754080000001</v>
+        <v>-0.4441893120000002</v>
       </c>
       <c r="P29">
-        <v>-1.228726224</v>
+        <v>-1.332567936000001</v>
       </c>
       <c r="Q29">
-        <v>-1.698726224000001</v>
+        <v>-1.802567936000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2057989111069359</v>
+        <v>0.2080211182056434</v>
       </c>
       <c r="T29">
-        <v>1.547311754755074</v>
+        <v>1.568802195793339</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1404381057713429</v>
+        <v>0.1354224591366521</v>
       </c>
       <c r="W29">
-        <v>0.1726000283611143</v>
+        <v>0.1736071702053603</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5617524230853718</v>
+        <v>0.5416898365466085</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1983852127655641</v>
+        <v>0.1999352127655641</v>
       </c>
       <c r="C30">
-        <v>35.59253114603872</v>
+        <v>34.35270995428333</v>
       </c>
       <c r="D30">
-        <v>54.72309114603872</v>
+        <v>54.17278995428333</v>
       </c>
       <c r="E30">
-        <v>18.75456000000001</v>
+        <v>19.44408000000001</v>
       </c>
       <c r="F30">
-        <v>19.30656</v>
+        <v>19.99608000000001</v>
       </c>
       <c r="G30">
         <v>0.176</v>
@@ -3747,37 +3747,37 @@
         <v>2.1</v>
       </c>
       <c r="M30">
-        <v>3.876757248000001</v>
+        <v>4.015212864000001</v>
       </c>
       <c r="N30">
-        <v>-1.776757248000001</v>
+        <v>-1.915212864000001</v>
       </c>
       <c r="O30">
-        <v>-0.4441893120000002</v>
+        <v>-0.4788032160000003</v>
       </c>
       <c r="P30">
-        <v>-1.332567936000001</v>
+        <v>-1.436409648000001</v>
       </c>
       <c r="Q30">
-        <v>-1.802567936000001</v>
+        <v>-1.906409648000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2080211182056434</v>
+        <v>0.210305922687413</v>
       </c>
       <c r="T30">
-        <v>1.568802195793339</v>
+        <v>1.590898001367893</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1354224591366521</v>
+        <v>0.1307527191664227</v>
       </c>
       <c r="W30">
-        <v>0.1736071702053603</v>
+        <v>0.1745448539913823</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5416898365466085</v>
+        <v>0.5230108766656909</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1999352127655641</v>
+        <v>0.2014852127655641</v>
       </c>
       <c r="C31">
-        <v>34.35270995428333</v>
+        <v>33.12384634587282</v>
       </c>
       <c r="D31">
-        <v>54.17278995428333</v>
+        <v>53.63344634587282</v>
       </c>
       <c r="E31">
-        <v>19.44408</v>
+        <v>20.1336</v>
       </c>
       <c r="F31">
-        <v>19.99608</v>
+        <v>20.6856</v>
       </c>
       <c r="G31">
         <v>0.176</v>
@@ -3829,37 +3829,37 @@
         <v>2.1</v>
       </c>
       <c r="M31">
-        <v>4.015212864</v>
+        <v>4.153668480000001</v>
       </c>
       <c r="N31">
-        <v>-1.915212864</v>
+        <v>-2.053668480000001</v>
       </c>
       <c r="O31">
-        <v>-0.4788032160000001</v>
+        <v>-0.5134171200000003</v>
       </c>
       <c r="P31">
-        <v>-1.436409648</v>
+        <v>-1.540251360000001</v>
       </c>
       <c r="Q31">
-        <v>-1.906409648</v>
+        <v>-2.010251360000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.210305922687413</v>
+        <v>0.2126560072972332</v>
       </c>
       <c r="T31">
-        <v>1.590898001367893</v>
+        <v>1.613625115673149</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1307527191664228</v>
+        <v>0.1263942951942086</v>
       </c>
       <c r="W31">
-        <v>0.1745448539913823</v>
+        <v>0.1754200255250029</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5230108766656909</v>
+        <v>0.5055771807768346</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2014852127655641</v>
+        <v>0.2145684962111786</v>
       </c>
       <c r="C32">
-        <v>33.12384634587282</v>
+        <v>28.27655047856769</v>
       </c>
       <c r="D32">
-        <v>53.63344634587282</v>
+        <v>49.47567047856769</v>
       </c>
       <c r="E32">
-        <v>20.1336</v>
+        <v>20.82312</v>
       </c>
       <c r="F32">
-        <v>20.6856</v>
+        <v>21.37512</v>
       </c>
       <c r="G32">
         <v>0.176</v>
@@ -3911,45 +3911,45 @@
         <v>2.1</v>
       </c>
       <c r="M32">
-        <v>4.153668480000001</v>
+        <v>5.040253296</v>
       </c>
       <c r="N32">
-        <v>-2.053668480000001</v>
+        <v>-2.940253296</v>
       </c>
       <c r="O32">
-        <v>-0.5134171200000003</v>
+        <v>-0.7350633240000001</v>
       </c>
       <c r="P32">
-        <v>-1.540251360000001</v>
+        <v>-2.205189972</v>
       </c>
       <c r="Q32">
-        <v>-2.010251360000001</v>
+        <v>-2.675189972000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2126560072972332</v>
+        <v>0.2160644761647504</v>
       </c>
       <c r="T32">
-        <v>1.613625115673149</v>
+        <v>1.64658761465479</v>
       </c>
       <c r="U32">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.1263942951942086</v>
+        <v>0.1041614318107079</v>
       </c>
       <c r="W32">
-        <v>0.1754200255250029</v>
+        <v>0.2112387343790351</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.5055771807768346</v>
+        <v>0.4166457272428318</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2145684962111786</v>
+        <v>0.2164684962111786</v>
       </c>
       <c r="C33">
-        <v>28.27655047856769</v>
+        <v>27.03623302035982</v>
       </c>
       <c r="D33">
-        <v>49.47567047856769</v>
+        <v>48.92487302035983</v>
       </c>
       <c r="E33">
-        <v>20.82312</v>
+        <v>21.51264</v>
       </c>
       <c r="F33">
-        <v>21.37512</v>
+        <v>22.06464</v>
       </c>
       <c r="G33">
         <v>0.176</v>
@@ -3993,37 +3993,37 @@
         <v>2.1</v>
       </c>
       <c r="M33">
-        <v>5.040253296</v>
+        <v>5.202842112000001</v>
       </c>
       <c r="N33">
-        <v>-2.940253296</v>
+        <v>-3.102842112000001</v>
       </c>
       <c r="O33">
-        <v>-0.7350633240000001</v>
+        <v>-0.7757105280000002</v>
       </c>
       <c r="P33">
-        <v>-2.205189972</v>
+        <v>-2.327131584</v>
       </c>
       <c r="Q33">
-        <v>-2.675189972000001</v>
+        <v>-2.797131584000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2160644761647504</v>
+        <v>0.2185683655201143</v>
       </c>
       <c r="T33">
-        <v>1.64658761465479</v>
+        <v>1.670802138399713</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.1041614318107079</v>
+        <v>0.1009063870666233</v>
       </c>
       <c r="W33">
-        <v>0.2112387343790351</v>
+        <v>0.2120062739296902</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.4166457272428318</v>
+        <v>0.4036255482664932</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2164684962111786</v>
+        <v>0.2183684962111787</v>
       </c>
       <c r="C34">
-        <v>27.03623302035982</v>
+        <v>25.80804425532097</v>
       </c>
       <c r="D34">
-        <v>48.92487302035983</v>
+        <v>48.38620425532098</v>
       </c>
       <c r="E34">
-        <v>21.51264</v>
+        <v>22.20216000000001</v>
       </c>
       <c r="F34">
-        <v>22.06464</v>
+        <v>22.75416000000001</v>
       </c>
       <c r="G34">
         <v>0.176</v>
@@ -4075,37 +4075,37 @@
         <v>2.1</v>
       </c>
       <c r="M34">
-        <v>5.202842112000001</v>
+        <v>5.365430928000001</v>
       </c>
       <c r="N34">
-        <v>-3.102842112000001</v>
+        <v>-3.265430928000001</v>
       </c>
       <c r="O34">
-        <v>-0.7757105280000002</v>
+        <v>-0.8163577320000003</v>
       </c>
       <c r="P34">
-        <v>-2.327131584</v>
+        <v>-2.449073196000001</v>
       </c>
       <c r="Q34">
-        <v>-2.797131584000001</v>
+        <v>-2.919073196000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2185683655201143</v>
+        <v>0.2211469978413101</v>
       </c>
       <c r="T34">
-        <v>1.670802138399713</v>
+        <v>1.695739483748963</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1009063870666233</v>
+        <v>0.09784861776157412</v>
       </c>
       <c r="W34">
-        <v>0.2120062739296902</v>
+        <v>0.2127272959318208</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.4036255482664932</v>
+        <v>0.3913944710462964</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2183684962111787</v>
+        <v>0.2202684962111786</v>
       </c>
       <c r="C35">
-        <v>25.80804425532097</v>
+        <v>24.59158793110442</v>
       </c>
       <c r="D35">
-        <v>48.38620425532098</v>
+        <v>47.85926793110443</v>
       </c>
       <c r="E35">
-        <v>22.20216000000001</v>
+        <v>22.89168000000001</v>
       </c>
       <c r="F35">
-        <v>22.75416000000001</v>
+        <v>23.44368000000001</v>
       </c>
       <c r="G35">
         <v>0.176</v>
@@ -4157,37 +4157,37 @@
         <v>2.1</v>
       </c>
       <c r="M35">
-        <v>5.365430928000001</v>
+        <v>5.528019744000002</v>
       </c>
       <c r="N35">
-        <v>-3.265430928000001</v>
+        <v>-3.428019744000002</v>
       </c>
       <c r="O35">
-        <v>-0.8163577320000003</v>
+        <v>-0.8570049360000004</v>
       </c>
       <c r="P35">
-        <v>-2.449073196000001</v>
+        <v>-2.571014808000001</v>
       </c>
       <c r="Q35">
-        <v>-2.919073196000001</v>
+        <v>-3.041014808000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2211469978413101</v>
+        <v>0.2238037705358754</v>
       </c>
       <c r="T35">
-        <v>1.695739483748963</v>
+        <v>1.721432506230008</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.09784861776157412</v>
+        <v>0.09497071723917487</v>
       </c>
       <c r="W35">
-        <v>0.2127272959318208</v>
+        <v>0.2134059048750026</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3913944710462964</v>
+        <v>0.3798828689566995</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2202684962111786</v>
+        <v>0.2221684962111786</v>
       </c>
       <c r="C36">
-        <v>24.59158793110442</v>
+        <v>23.38648487050941</v>
       </c>
       <c r="D36">
-        <v>47.85926793110443</v>
+        <v>47.34368487050941</v>
       </c>
       <c r="E36">
-        <v>22.89168000000001</v>
+        <v>23.58120000000001</v>
       </c>
       <c r="F36">
-        <v>23.44368000000001</v>
+        <v>24.13320000000001</v>
       </c>
       <c r="G36">
         <v>0.176</v>
@@ -4239,37 +4239,37 @@
         <v>2.1</v>
       </c>
       <c r="M36">
-        <v>5.528019744000002</v>
+        <v>5.690608560000001</v>
       </c>
       <c r="N36">
-        <v>-3.428019744000002</v>
+        <v>-3.590608560000001</v>
       </c>
       <c r="O36">
-        <v>-0.8570049360000004</v>
+        <v>-0.8976521400000003</v>
       </c>
       <c r="P36">
-        <v>-2.571014808000001</v>
+        <v>-2.692956420000001</v>
       </c>
       <c r="Q36">
-        <v>-3.041014808000001</v>
+        <v>-3.162956420000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2238037705358754</v>
+        <v>0.2265422900825812</v>
       </c>
       <c r="T36">
-        <v>1.721432506230008</v>
+        <v>1.747916083248931</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.09497071723917487</v>
+        <v>0.09225726817519846</v>
       </c>
       <c r="W36">
-        <v>0.2134059048750026</v>
+        <v>0.2140457361642882</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3798828689566995</v>
+        <v>0.3690290727007939</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2221684962111786</v>
+        <v>0.2240684962111786</v>
       </c>
       <c r="C37">
-        <v>23.38648487050941</v>
+        <v>22.1923720615399</v>
       </c>
       <c r="D37">
-        <v>47.34368487050941</v>
+        <v>46.83909206153991</v>
       </c>
       <c r="E37">
-        <v>23.58120000000001</v>
+        <v>24.27072000000001</v>
       </c>
       <c r="F37">
-        <v>24.13320000000001</v>
+        <v>24.82272000000001</v>
       </c>
       <c r="G37">
         <v>0.176</v>
@@ -4321,37 +4321,37 @@
         <v>2.1</v>
       </c>
       <c r="M37">
-        <v>5.690608560000001</v>
+        <v>5.853197376000002</v>
       </c>
       <c r="N37">
-        <v>-3.590608560000001</v>
+        <v>-3.753197376000001</v>
       </c>
       <c r="O37">
-        <v>-0.8976521400000003</v>
+        <v>-0.9382993440000004</v>
       </c>
       <c r="P37">
-        <v>-2.692956420000001</v>
+        <v>-2.814898032000001</v>
       </c>
       <c r="Q37">
-        <v>-3.162956420000001</v>
+        <v>-3.284898032000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2265422900825812</v>
+        <v>0.2293663883651215</v>
       </c>
       <c r="T37">
-        <v>1.747916083248931</v>
+        <v>1.775227272049695</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.09225726817519846</v>
+        <v>0.08969456628144294</v>
       </c>
       <c r="W37">
-        <v>0.2140457361642882</v>
+        <v>0.2146500212708358</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3690290727007939</v>
+        <v>0.3587782651257717</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2240684962111786</v>
+        <v>0.2259684962111786</v>
       </c>
       <c r="C38">
-        <v>22.19237206153991</v>
+        <v>21.00890180503882</v>
       </c>
       <c r="D38">
-        <v>46.83909206153991</v>
+        <v>46.34514180503882</v>
       </c>
       <c r="E38">
-        <v>24.27072</v>
+        <v>24.96024000000001</v>
       </c>
       <c r="F38">
-        <v>24.82272</v>
+        <v>25.51224000000001</v>
       </c>
       <c r="G38">
         <v>0.176</v>
@@ -4403,37 +4403,37 @@
         <v>2.1</v>
       </c>
       <c r="M38">
-        <v>5.853197376000002</v>
+        <v>6.015786192000002</v>
       </c>
       <c r="N38">
-        <v>-3.753197376000001</v>
+        <v>-3.915786192000002</v>
       </c>
       <c r="O38">
-        <v>-0.9382993440000004</v>
+        <v>-0.9789465480000005</v>
       </c>
       <c r="P38">
-        <v>-2.814898032000001</v>
+        <v>-2.936839644000001</v>
       </c>
       <c r="Q38">
-        <v>-3.284898032000001</v>
+        <v>-3.406839644000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2293663883651215</v>
+        <v>0.2322801405613933</v>
       </c>
       <c r="T38">
-        <v>1.775227272049695</v>
+        <v>1.803405482717151</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.08969456628144294</v>
+        <v>0.0872703888143769</v>
       </c>
       <c r="W38">
-        <v>0.2146500212708358</v>
+        <v>0.2152216423175699</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3587782651257717</v>
+        <v>0.3490815552575076</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2259684962111786</v>
+        <v>0.2278684962111786</v>
       </c>
       <c r="C39">
-        <v>21.00890180503882</v>
+        <v>19.83574091569222</v>
       </c>
       <c r="D39">
-        <v>46.34514180503882</v>
+        <v>45.86150091569223</v>
       </c>
       <c r="E39">
-        <v>24.96024000000001</v>
+        <v>25.64976</v>
       </c>
       <c r="F39">
-        <v>25.51224000000001</v>
+        <v>26.20176</v>
       </c>
       <c r="G39">
         <v>0.176</v>
@@ -4485,37 +4485,37 @@
         <v>2.1</v>
       </c>
       <c r="M39">
-        <v>6.015786192000002</v>
+        <v>6.178375008000002</v>
       </c>
       <c r="N39">
-        <v>-3.915786192000002</v>
+        <v>-4.078375008000002</v>
       </c>
       <c r="O39">
-        <v>-0.9789465480000005</v>
+        <v>-1.019593752</v>
       </c>
       <c r="P39">
-        <v>-2.936839644000001</v>
+        <v>-3.058781256000001</v>
       </c>
       <c r="Q39">
-        <v>-3.406839644000001</v>
+        <v>-3.528781256000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2322801405613933</v>
+        <v>0.2352878847639964</v>
       </c>
       <c r="T39">
-        <v>1.803405482717151</v>
+        <v>1.832492667922266</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0872703888143769</v>
+        <v>0.08497379963505121</v>
       </c>
       <c r="W39">
-        <v>0.2152216423175699</v>
+        <v>0.2157631780460549</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3490815552575076</v>
+        <v>0.3398951985402048</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2278684962111786</v>
+        <v>0.2297684962111786</v>
       </c>
       <c r="C40">
-        <v>19.83574091569222</v>
+        <v>18.67256997254492</v>
       </c>
       <c r="D40">
-        <v>45.86150091569223</v>
+        <v>45.38784997254493</v>
       </c>
       <c r="E40">
-        <v>25.64976</v>
+        <v>26.33928000000001</v>
       </c>
       <c r="F40">
-        <v>26.20176</v>
+        <v>26.89128000000001</v>
       </c>
       <c r="G40">
         <v>0.176</v>
@@ -4567,37 +4567,37 @@
         <v>2.1</v>
       </c>
       <c r="M40">
-        <v>6.178375008000002</v>
+        <v>6.340963824000002</v>
       </c>
       <c r="N40">
-        <v>-4.078375008000002</v>
+        <v>-4.240963824000001</v>
       </c>
       <c r="O40">
-        <v>-1.019593752</v>
+        <v>-1.060240956</v>
       </c>
       <c r="P40">
-        <v>-3.058781256000001</v>
+        <v>-3.180722868000001</v>
       </c>
       <c r="Q40">
-        <v>-3.528781256000002</v>
+        <v>-3.650722868000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2352878847639964</v>
+        <v>0.2383942435306192</v>
       </c>
       <c r="T40">
-        <v>1.832492667922266</v>
+        <v>1.862533531330828</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08497379963505121</v>
+        <v>0.08279498425979348</v>
       </c>
       <c r="W40">
-        <v>0.2157631780460549</v>
+        <v>0.2162769427115407</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3398951985402048</v>
+        <v>0.331179937039174</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2297684962111786</v>
+        <v>0.2316684962111786</v>
       </c>
       <c r="C41">
-        <v>18.67256997254492</v>
+        <v>17.51908261548482</v>
       </c>
       <c r="D41">
-        <v>45.38784997254493</v>
+        <v>44.92388261548482</v>
       </c>
       <c r="E41">
-        <v>26.33928000000001</v>
+        <v>27.02880000000001</v>
       </c>
       <c r="F41">
-        <v>26.89128000000001</v>
+        <v>27.58080000000001</v>
       </c>
       <c r="G41">
         <v>0.176</v>
@@ -4649,37 +4649,37 @@
         <v>2.1</v>
       </c>
       <c r="M41">
-        <v>6.340963824000002</v>
+        <v>6.503552640000002</v>
       </c>
       <c r="N41">
-        <v>-4.240963824000001</v>
+        <v>-4.403552640000003</v>
       </c>
       <c r="O41">
-        <v>-1.060240956</v>
+        <v>-1.100888160000001</v>
       </c>
       <c r="P41">
-        <v>-3.180722868000001</v>
+        <v>-3.302664480000002</v>
       </c>
       <c r="Q41">
-        <v>-3.650722868000001</v>
+        <v>-3.772664480000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2383942435306192</v>
+        <v>0.2416041475894629</v>
       </c>
       <c r="T41">
-        <v>1.862533531330828</v>
+        <v>1.893575756853008</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08279498425979348</v>
+        <v>0.08072510965329864</v>
       </c>
       <c r="W41">
-        <v>0.2162769427115407</v>
+        <v>0.2167650191437522</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.331179937039174</v>
+        <v>0.3229004386131945</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2316684962111786</v>
+        <v>0.2335684962111786</v>
       </c>
       <c r="C42">
-        <v>17.51908261548482</v>
+        <v>16.37498488443977</v>
       </c>
       <c r="D42">
-        <v>44.92388261548482</v>
+        <v>44.46930488443977</v>
       </c>
       <c r="E42">
-        <v>27.02880000000001</v>
+        <v>27.71832000000001</v>
       </c>
       <c r="F42">
-        <v>27.58080000000001</v>
+        <v>28.27032000000001</v>
       </c>
       <c r="G42">
         <v>0.176</v>
@@ -4731,37 +4731,37 @@
         <v>2.1</v>
       </c>
       <c r="M42">
-        <v>6.503552640000002</v>
+        <v>6.666141456000003</v>
       </c>
       <c r="N42">
-        <v>-4.403552640000003</v>
+        <v>-4.566141456000002</v>
       </c>
       <c r="O42">
-        <v>-1.100888160000001</v>
+        <v>-1.141535364000001</v>
       </c>
       <c r="P42">
-        <v>-3.302664480000002</v>
+        <v>-3.424606092000002</v>
       </c>
       <c r="Q42">
-        <v>-3.772664480000002</v>
+        <v>-3.894606092000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2416041475894629</v>
+        <v>0.244922861955386</v>
       </c>
       <c r="T42">
-        <v>1.893575756853008</v>
+        <v>1.925670261206449</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08072510965329864</v>
+        <v>0.07875620453980355</v>
       </c>
       <c r="W42">
-        <v>0.2167650191437522</v>
+        <v>0.2172292869695143</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3229004386131945</v>
+        <v>0.3150248181592142</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2335684962111786</v>
+        <v>0.2354684962111787</v>
       </c>
       <c r="C43">
-        <v>16.37498488443977</v>
+        <v>15.23999459829185</v>
       </c>
       <c r="D43">
-        <v>44.46930488443977</v>
+        <v>44.02383459829186</v>
       </c>
       <c r="E43">
-        <v>27.71832000000001</v>
+        <v>28.40784000000001</v>
       </c>
       <c r="F43">
-        <v>28.27032000000001</v>
+        <v>28.95984000000001</v>
       </c>
       <c r="G43">
         <v>0.176</v>
@@ -4813,37 +4813,37 @@
         <v>2.1</v>
       </c>
       <c r="M43">
-        <v>6.666141456000003</v>
+        <v>6.828730272000002</v>
       </c>
       <c r="N43">
-        <v>-4.566141456000002</v>
+        <v>-4.728730272000002</v>
       </c>
       <c r="O43">
-        <v>-1.141535364000001</v>
+        <v>-1.182182568</v>
       </c>
       <c r="P43">
-        <v>-3.424606092000002</v>
+        <v>-3.546547704000001</v>
       </c>
       <c r="Q43">
-        <v>-3.894606092000002</v>
+        <v>-4.016547704000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.244922861955386</v>
+        <v>0.2483560147477203</v>
       </c>
       <c r="T43">
-        <v>1.925670261206449</v>
+        <v>1.95887147260656</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07875620453980355</v>
+        <v>0.07688105681266537</v>
       </c>
       <c r="W43">
-        <v>0.2172292869695143</v>
+        <v>0.2176714468035735</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3150248181592142</v>
+        <v>0.3075242272506615</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2354684962111786</v>
+        <v>0.2373684962111786</v>
       </c>
       <c r="C44">
-        <v>15.23999459829187</v>
+        <v>14.11384077075193</v>
       </c>
       <c r="D44">
-        <v>44.02383459829187</v>
+        <v>43.58720077075193</v>
       </c>
       <c r="E44">
-        <v>28.40784</v>
+        <v>29.09736000000001</v>
       </c>
       <c r="F44">
-        <v>28.95984</v>
+        <v>29.64936000000001</v>
       </c>
       <c r="G44">
         <v>0.176</v>
@@ -4895,37 +4895,37 @@
         <v>2.1</v>
       </c>
       <c r="M44">
-        <v>6.828730272000001</v>
+        <v>6.991319088000002</v>
       </c>
       <c r="N44">
-        <v>-4.728730272000002</v>
+        <v>-4.891319088000001</v>
       </c>
       <c r="O44">
-        <v>-1.182182568</v>
+        <v>-1.222829772</v>
       </c>
       <c r="P44">
-        <v>-3.546547704000001</v>
+        <v>-3.668489316000001</v>
       </c>
       <c r="Q44">
-        <v>-4.016547704000001</v>
+        <v>-4.138489316000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2483560147477202</v>
+        <v>0.2519096290415399</v>
       </c>
       <c r="T44">
-        <v>1.95887147260656</v>
+        <v>1.99323763879264</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07688105681266538</v>
+        <v>0.07509312525888245</v>
       </c>
       <c r="W44">
-        <v>0.2176714468035735</v>
+        <v>0.2180930410639555</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3075242272506614</v>
+        <v>0.3003725010355299</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2373684962111786</v>
+        <v>0.2392684962111786</v>
       </c>
       <c r="C45">
-        <v>14.11384077075193</v>
+        <v>12.99626306065307</v>
       </c>
       <c r="D45">
-        <v>43.58720077075193</v>
+        <v>43.15914306065307</v>
       </c>
       <c r="E45">
-        <v>29.09736000000001</v>
+        <v>29.78688000000001</v>
       </c>
       <c r="F45">
-        <v>29.64936000000001</v>
+        <v>30.33888000000001</v>
       </c>
       <c r="G45">
         <v>0.176</v>
@@ -4977,37 +4977,37 @@
         <v>2.1</v>
       </c>
       <c r="M45">
-        <v>6.991319088000002</v>
+        <v>7.153907904000002</v>
       </c>
       <c r="N45">
-        <v>-4.891319088000001</v>
+        <v>-5.053907904000003</v>
       </c>
       <c r="O45">
-        <v>-1.222829772</v>
+        <v>-1.263476976000001</v>
       </c>
       <c r="P45">
-        <v>-3.668489316000001</v>
+        <v>-3.790430928000002</v>
       </c>
       <c r="Q45">
-        <v>-4.138489316000001</v>
+        <v>-4.260430928000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2519096290415399</v>
+        <v>0.2555901581315674</v>
       </c>
       <c r="T45">
-        <v>1.99323763879264</v>
+        <v>2.028831168056794</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07509312525888245</v>
+        <v>0.07338646332118058</v>
       </c>
       <c r="W45">
-        <v>0.2180930410639555</v>
+        <v>0.2184954719488656</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3003725010355299</v>
+        <v>0.2935458532847223</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2392684962111786</v>
+        <v>0.2411684962111786</v>
       </c>
       <c r="C46">
-        <v>12.99626306065307</v>
+        <v>11.88701125432028</v>
       </c>
       <c r="D46">
-        <v>43.15914306065307</v>
+        <v>42.73941125432028</v>
       </c>
       <c r="E46">
-        <v>29.78688000000001</v>
+        <v>30.47640000000001</v>
       </c>
       <c r="F46">
-        <v>30.33888000000001</v>
+        <v>31.0284</v>
       </c>
       <c r="G46">
         <v>0.176</v>
@@ -5059,37 +5059,37 @@
         <v>2.1</v>
       </c>
       <c r="M46">
-        <v>7.153907904000002</v>
+        <v>7.316496720000002</v>
       </c>
       <c r="N46">
-        <v>-5.053907904000003</v>
+        <v>-5.216496720000002</v>
       </c>
       <c r="O46">
-        <v>-1.263476976000001</v>
+        <v>-1.304124180000001</v>
       </c>
       <c r="P46">
-        <v>-3.790430928000002</v>
+        <v>-3.912372540000002</v>
       </c>
       <c r="Q46">
-        <v>-4.260430928000002</v>
+        <v>-4.382372540000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2555901581315674</v>
+        <v>0.2594045246430504</v>
       </c>
       <c r="T46">
-        <v>2.028831168056794</v>
+        <v>2.065719007476009</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07338646332118058</v>
+        <v>0.07175565302515435</v>
       </c>
       <c r="W46">
-        <v>0.2184954719488656</v>
+        <v>0.2188800170166686</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2935458532847223</v>
+        <v>0.2870226121006173</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2411684962111786</v>
+        <v>0.2430684962111786</v>
       </c>
       <c r="C47">
-        <v>11.88701125432028</v>
+        <v>10.78584477785361</v>
       </c>
       <c r="D47">
-        <v>42.73941125432028</v>
+        <v>42.32776477785362</v>
       </c>
       <c r="E47">
-        <v>30.47640000000001</v>
+        <v>31.16592000000001</v>
       </c>
       <c r="F47">
-        <v>31.0284</v>
+        <v>31.71792000000001</v>
       </c>
       <c r="G47">
         <v>0.176</v>
@@ -5141,37 +5141,37 @@
         <v>2.1</v>
       </c>
       <c r="M47">
-        <v>7.316496720000002</v>
+        <v>7.479085536000002</v>
       </c>
       <c r="N47">
-        <v>-5.216496720000002</v>
+        <v>-5.379085536000002</v>
       </c>
       <c r="O47">
-        <v>-1.304124180000001</v>
+        <v>-1.344771384</v>
       </c>
       <c r="P47">
-        <v>-3.912372540000002</v>
+        <v>-4.034314152000001</v>
       </c>
       <c r="Q47">
-        <v>-4.382372540000002</v>
+        <v>-4.504314152000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2594045246430504</v>
+        <v>0.2633601639882921</v>
       </c>
       <c r="T47">
-        <v>2.065719007476009</v>
+        <v>2.103973063170009</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07175565302515435</v>
+        <v>0.07019574752460751</v>
       </c>
       <c r="W47">
-        <v>0.2188800170166686</v>
+        <v>0.2192478427336975</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2870226121006173</v>
+        <v>0.2807829900984301</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2430684962111786</v>
+        <v>0.2449684962111786</v>
       </c>
       <c r="C48">
-        <v>10.78584477785361</v>
+        <v>9.692532237327264</v>
       </c>
       <c r="D48">
-        <v>42.32776477785362</v>
+        <v>41.92397223732727</v>
       </c>
       <c r="E48">
-        <v>31.16592000000001</v>
+        <v>31.85544000000001</v>
       </c>
       <c r="F48">
-        <v>31.71792000000001</v>
+        <v>32.40744000000001</v>
       </c>
       <c r="G48">
         <v>0.176</v>
@@ -5223,37 +5223,37 @@
         <v>2.1</v>
       </c>
       <c r="M48">
-        <v>7.479085536000002</v>
+        <v>7.641674352000003</v>
       </c>
       <c r="N48">
-        <v>-5.379085536000002</v>
+        <v>-5.541674352000003</v>
       </c>
       <c r="O48">
-        <v>-1.344771384</v>
+        <v>-1.385418588000001</v>
       </c>
       <c r="P48">
-        <v>-4.034314152000001</v>
+        <v>-4.156255764000003</v>
       </c>
       <c r="Q48">
-        <v>-4.504314152000001</v>
+        <v>-4.626255764000003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2633601639882921</v>
+        <v>0.2674650727427882</v>
       </c>
       <c r="T48">
-        <v>2.103973063170009</v>
+        <v>2.143670668135481</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07019574752460751</v>
+        <v>0.06870222098153075</v>
       </c>
       <c r="W48">
-        <v>0.2192478427336975</v>
+        <v>0.219600016292555</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2807829900984301</v>
+        <v>0.274808883926123</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2449684962111786</v>
+        <v>0.2468684962111787</v>
       </c>
       <c r="C49">
-        <v>9.692532237327264</v>
+        <v>8.606850985057982</v>
       </c>
       <c r="D49">
-        <v>41.92397223732727</v>
+        <v>41.52781098505799</v>
       </c>
       <c r="E49">
-        <v>31.85544000000001</v>
+        <v>32.54496000000001</v>
       </c>
       <c r="F49">
-        <v>32.40744000000001</v>
+        <v>33.09696000000001</v>
       </c>
       <c r="G49">
         <v>0.176</v>
@@ -5305,37 +5305,37 @@
         <v>2.1</v>
       </c>
       <c r="M49">
-        <v>7.641674352000003</v>
+        <v>7.804263168000003</v>
       </c>
       <c r="N49">
-        <v>-5.541674352000003</v>
+        <v>-5.704263168000002</v>
       </c>
       <c r="O49">
-        <v>-1.385418588000001</v>
+        <v>-1.426065792000001</v>
       </c>
       <c r="P49">
-        <v>-4.156255764000003</v>
+        <v>-4.278197376000001</v>
       </c>
       <c r="Q49">
-        <v>-4.626255764000003</v>
+        <v>-4.748197376000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2674650727427882</v>
+        <v>0.2717278626032265</v>
       </c>
       <c r="T49">
-        <v>2.143670668135481</v>
+        <v>2.184895104061163</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06870222098153075</v>
+        <v>0.06727092471108219</v>
       </c>
       <c r="W49">
-        <v>0.219600016292555</v>
+        <v>0.2199375159531268</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.274808883926123</v>
+        <v>0.2690836988443288</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2468684962111786</v>
+        <v>0.2487684962111786</v>
       </c>
       <c r="C50">
-        <v>8.606850985057989</v>
+        <v>7.528586710234599</v>
       </c>
       <c r="D50">
-        <v>41.52781098505799</v>
+        <v>41.1390667102346</v>
       </c>
       <c r="E50">
-        <v>32.54496</v>
+        <v>33.23448</v>
       </c>
       <c r="F50">
-        <v>33.09696</v>
+        <v>33.78648</v>
       </c>
       <c r="G50">
         <v>0.176</v>
@@ -5387,37 +5387,37 @@
         <v>2.1</v>
       </c>
       <c r="M50">
-        <v>7.804263168000001</v>
+        <v>7.966851984000002</v>
       </c>
       <c r="N50">
-        <v>-5.704263168000001</v>
+        <v>-5.866851984000002</v>
       </c>
       <c r="O50">
-        <v>-1.426065792</v>
+        <v>-1.466712996</v>
       </c>
       <c r="P50">
-        <v>-4.278197376</v>
+        <v>-4.400138988000002</v>
       </c>
       <c r="Q50">
-        <v>-4.748197376</v>
+        <v>-4.870138988000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2717278626032264</v>
+        <v>0.2761578206934857</v>
       </c>
       <c r="T50">
-        <v>2.184895104061163</v>
+        <v>2.22773618453295</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06727092471108222</v>
+        <v>0.06589804869657033</v>
       </c>
       <c r="W50">
-        <v>0.2199375159531268</v>
+        <v>0.2202612401173487</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2690836988443289</v>
+        <v>0.2635921947862813</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2487684962111786</v>
+        <v>0.2506684962111786</v>
       </c>
       <c r="C51">
-        <v>7.528586710234599</v>
+        <v>6.457533052327165</v>
       </c>
       <c r="D51">
-        <v>41.1390667102346</v>
+        <v>40.75753305232717</v>
       </c>
       <c r="E51">
-        <v>33.23448</v>
+        <v>33.92400000000001</v>
       </c>
       <c r="F51">
-        <v>33.78648</v>
+        <v>34.47600000000001</v>
       </c>
       <c r="G51">
         <v>0.176</v>
@@ -5469,37 +5469,37 @@
         <v>2.1</v>
       </c>
       <c r="M51">
-        <v>7.966851984000002</v>
+        <v>8.129440800000001</v>
       </c>
       <c r="N51">
-        <v>-5.866851984000002</v>
+        <v>-6.029440800000001</v>
       </c>
       <c r="O51">
-        <v>-1.466712996</v>
+        <v>-1.5073602</v>
       </c>
       <c r="P51">
-        <v>-4.400138988000002</v>
+        <v>-4.522080600000001</v>
       </c>
       <c r="Q51">
-        <v>-4.870138988000003</v>
+        <v>-4.992080600000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2761578206934857</v>
+        <v>0.2807649771073555</v>
       </c>
       <c r="T51">
-        <v>2.22773618453295</v>
+        <v>2.27229090822361</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06589804869657033</v>
+        <v>0.06458008772263893</v>
       </c>
       <c r="W51">
-        <v>0.2202612401173487</v>
+        <v>0.2205720153150018</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2635921947862813</v>
+        <v>0.2583203508905556</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2506684962111786</v>
+        <v>0.2525684962111786</v>
       </c>
       <c r="C52">
-        <v>6.457533052327165</v>
+        <v>5.393491235810536</v>
       </c>
       <c r="D52">
-        <v>40.75753305232717</v>
+        <v>40.38301123581054</v>
       </c>
       <c r="E52">
-        <v>33.92400000000001</v>
+        <v>34.61352000000001</v>
       </c>
       <c r="F52">
-        <v>34.47600000000001</v>
+        <v>35.16552000000001</v>
       </c>
       <c r="G52">
         <v>0.176</v>
@@ -5551,37 +5551,37 @@
         <v>2.1</v>
       </c>
       <c r="M52">
-        <v>8.129440800000001</v>
+        <v>8.292029616000002</v>
       </c>
       <c r="N52">
-        <v>-6.029440800000001</v>
+        <v>-6.192029616000003</v>
       </c>
       <c r="O52">
-        <v>-1.5073602</v>
+        <v>-1.548007404000001</v>
       </c>
       <c r="P52">
-        <v>-4.522080600000001</v>
+        <v>-4.644022212000002</v>
       </c>
       <c r="Q52">
-        <v>-4.992080600000001</v>
+        <v>-5.114022212000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2807649771073555</v>
+        <v>0.2855601807217913</v>
       </c>
       <c r="T52">
-        <v>2.27229090822361</v>
+        <v>2.318664192064908</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06458008772263893</v>
+        <v>0.06331381149278324</v>
       </c>
       <c r="W52">
-        <v>0.2205720153150018</v>
+        <v>0.2208706032500017</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2583203508905556</v>
+        <v>0.2532552459711329</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2525684962111786</v>
+        <v>0.2544684962111786</v>
       </c>
       <c r="C53">
-        <v>5.393491235810536</v>
+        <v>4.336269724843639</v>
       </c>
       <c r="D53">
-        <v>40.38301123581054</v>
+        <v>40.01530972484365</v>
       </c>
       <c r="E53">
-        <v>34.61352000000001</v>
+        <v>35.30304000000001</v>
       </c>
       <c r="F53">
-        <v>35.16552000000001</v>
+        <v>35.85504000000001</v>
       </c>
       <c r="G53">
         <v>0.176</v>
@@ -5633,37 +5633,37 @@
         <v>2.1</v>
       </c>
       <c r="M53">
-        <v>8.292029616000002</v>
+        <v>8.454618432000002</v>
       </c>
       <c r="N53">
-        <v>-6.192029616000003</v>
+        <v>-6.354618432000002</v>
       </c>
       <c r="O53">
-        <v>-1.548007404000001</v>
+        <v>-1.588654608000001</v>
       </c>
       <c r="P53">
-        <v>-4.644022212000002</v>
+        <v>-4.765963824000002</v>
       </c>
       <c r="Q53">
-        <v>-5.114022212000002</v>
+        <v>-5.235963824000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2855601807217913</v>
+        <v>0.2905551844868287</v>
       </c>
       <c r="T53">
-        <v>2.318664192064908</v>
+        <v>2.36696969606626</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06331381149278324</v>
+        <v>0.06209623819484511</v>
       </c>
       <c r="W53">
-        <v>0.2208706032500017</v>
+        <v>0.2211577070336555</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2532552459711329</v>
+        <v>0.2483849527793804</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2544684962111786</v>
+        <v>0.2563684962111786</v>
       </c>
       <c r="C54">
-        <v>4.336269724843639</v>
+        <v>3.285683896644173</v>
       </c>
       <c r="D54">
-        <v>40.01530972484365</v>
+        <v>39.65424389664418</v>
       </c>
       <c r="E54">
-        <v>35.30304000000001</v>
+        <v>35.99256000000001</v>
       </c>
       <c r="F54">
-        <v>35.85504000000001</v>
+        <v>36.54456000000001</v>
       </c>
       <c r="G54">
         <v>0.176</v>
@@ -5715,37 +5715,37 @@
         <v>2.1</v>
       </c>
       <c r="M54">
-        <v>8.454618432000002</v>
+        <v>8.617207248000003</v>
       </c>
       <c r="N54">
-        <v>-6.354618432000002</v>
+        <v>-6.517207248000004</v>
       </c>
       <c r="O54">
-        <v>-1.588654608000001</v>
+        <v>-1.629301812000001</v>
       </c>
       <c r="P54">
-        <v>-4.765963824000002</v>
+        <v>-4.887905436000002</v>
       </c>
       <c r="Q54">
-        <v>-5.235963824000002</v>
+        <v>-5.357905436000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2905551844868287</v>
+        <v>0.2957627416035697</v>
       </c>
       <c r="T54">
-        <v>2.36696969606626</v>
+        <v>2.417330753429372</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06209623819484511</v>
+        <v>0.06092461105909331</v>
       </c>
       <c r="W54">
-        <v>0.2211577070336555</v>
+        <v>0.2214339767122658</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2483849527793804</v>
+        <v>0.2436984442363732</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2563684962111786</v>
+        <v>0.2582684962111786</v>
       </c>
       <c r="C55">
-        <v>3.285683896644173</v>
+        <v>2.241555732388441</v>
       </c>
       <c r="D55">
-        <v>39.65424389664418</v>
+        <v>39.29963573238845</v>
       </c>
       <c r="E55">
-        <v>35.99256000000001</v>
+        <v>36.68208000000001</v>
       </c>
       <c r="F55">
-        <v>36.54456000000001</v>
+        <v>37.23408000000001</v>
       </c>
       <c r="G55">
         <v>0.176</v>
@@ -5797,37 +5797,37 @@
         <v>2.1</v>
       </c>
       <c r="M55">
-        <v>8.617207248000003</v>
+        <v>8.779796064000001</v>
       </c>
       <c r="N55">
-        <v>-6.517207248000004</v>
+        <v>-6.679796064000001</v>
       </c>
       <c r="O55">
-        <v>-1.629301812000001</v>
+        <v>-1.669949016</v>
       </c>
       <c r="P55">
-        <v>-4.887905436000002</v>
+        <v>-5.009847048000001</v>
       </c>
       <c r="Q55">
-        <v>-5.357905436000003</v>
+        <v>-5.479847048000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2957627416035697</v>
+        <v>0.3011967142471255</v>
       </c>
       <c r="T55">
-        <v>2.417330753429372</v>
+        <v>2.469881421982184</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06092461105909331</v>
+        <v>0.05979637752096197</v>
       </c>
       <c r="W55">
-        <v>0.2214339767122658</v>
+        <v>0.2217000141805572</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2436984442363732</v>
+        <v>0.2391855100838478</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2582684962111786</v>
+        <v>0.2601684962111787</v>
       </c>
       <c r="C56">
-        <v>2.241555732388441</v>
+        <v>1.203713524548803</v>
       </c>
       <c r="D56">
-        <v>39.29963573238845</v>
+        <v>38.95131352454881</v>
       </c>
       <c r="E56">
-        <v>36.68208000000001</v>
+        <v>37.37160000000001</v>
       </c>
       <c r="F56">
-        <v>37.23408000000001</v>
+        <v>37.92360000000001</v>
       </c>
       <c r="G56">
         <v>0.176</v>
@@ -5879,37 +5879,37 @@
         <v>2.1</v>
       </c>
       <c r="M56">
-        <v>8.779796064000001</v>
+        <v>8.942384880000002</v>
       </c>
       <c r="N56">
-        <v>-6.679796064000001</v>
+        <v>-6.842384880000003</v>
       </c>
       <c r="O56">
-        <v>-1.669949016</v>
+        <v>-1.710596220000001</v>
       </c>
       <c r="P56">
-        <v>-5.009847048000001</v>
+        <v>-5.131788660000002</v>
       </c>
       <c r="Q56">
-        <v>-5.479847048000002</v>
+        <v>-5.601788660000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3011967142471255</v>
+        <v>0.3068721967859506</v>
       </c>
       <c r="T56">
-        <v>2.469881421982184</v>
+        <v>2.524767675804011</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05979637752096197</v>
+        <v>0.05870917065694447</v>
       </c>
       <c r="W56">
-        <v>0.2217000141805572</v>
+        <v>0.2219563775590925</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2391855100838478</v>
+        <v>0.2348366826277778</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2601684962111787</v>
+        <v>0.2620684962111786</v>
       </c>
       <c r="C57">
-        <v>1.203713524548803</v>
+        <v>0.1719915996582912</v>
       </c>
       <c r="D57">
-        <v>38.95131352454881</v>
+        <v>38.6091115996583</v>
       </c>
       <c r="E57">
-        <v>37.37160000000001</v>
+        <v>38.06112000000001</v>
       </c>
       <c r="F57">
-        <v>37.92360000000001</v>
+        <v>38.61312000000001</v>
       </c>
       <c r="G57">
         <v>0.176</v>
@@ -5961,37 +5961,37 @@
         <v>2.1</v>
       </c>
       <c r="M57">
-        <v>8.942384880000002</v>
+        <v>9.104973696000002</v>
       </c>
       <c r="N57">
-        <v>-6.842384880000003</v>
+        <v>-7.004973696000002</v>
       </c>
       <c r="O57">
-        <v>-1.710596220000001</v>
+        <v>-1.751243424000001</v>
       </c>
       <c r="P57">
-        <v>-5.131788660000002</v>
+        <v>-5.253730272000002</v>
       </c>
       <c r="Q57">
-        <v>-5.601788660000002</v>
+        <v>-5.723730272000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3068721967859506</v>
+        <v>0.312805655803813</v>
       </c>
       <c r="T57">
-        <v>2.524767675804011</v>
+        <v>2.582148759345011</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05870917065694447</v>
+        <v>0.05766079260949904</v>
       </c>
       <c r="W57">
-        <v>0.2219563775590925</v>
+        <v>0.2222035851026801</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2348366826277778</v>
+        <v>0.2306431704379961</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2620684962111786</v>
+        <v>0.2639684962111787</v>
       </c>
       <c r="C58">
-        <v>0.1719915996582912</v>
+        <v>-0.8537699444386391</v>
       </c>
       <c r="D58">
-        <v>38.6091115996583</v>
+        <v>38.27287005556137</v>
       </c>
       <c r="E58">
-        <v>38.06112000000001</v>
+        <v>38.75064000000001</v>
       </c>
       <c r="F58">
-        <v>38.61312000000001</v>
+        <v>39.30264000000001</v>
       </c>
       <c r="G58">
         <v>0.176</v>
@@ -6043,37 +6043,37 @@
         <v>2.1</v>
       </c>
       <c r="M58">
-        <v>9.104973696000002</v>
+        <v>9.267562512000003</v>
       </c>
       <c r="N58">
-        <v>-7.004973696000002</v>
+        <v>-7.167562512000003</v>
       </c>
       <c r="O58">
-        <v>-1.751243424000001</v>
+        <v>-1.791890628000001</v>
       </c>
       <c r="P58">
-        <v>-5.253730272000002</v>
+        <v>-5.375671884000003</v>
       </c>
       <c r="Q58">
-        <v>-5.723730272000003</v>
+        <v>-5.845671884000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.312805655803813</v>
+        <v>0.3190150896597158</v>
       </c>
       <c r="T58">
-        <v>2.582148759345011</v>
+        <v>2.64219873049257</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05766079260949904</v>
+        <v>0.0566491997567008</v>
       </c>
       <c r="W58">
-        <v>0.2222035851026801</v>
+        <v>0.22244211869737</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2306431704379961</v>
+        <v>0.2265967990268032</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2639684962111787</v>
+        <v>0.2658684962111786</v>
       </c>
       <c r="C59">
-        <v>-0.8537699444386391</v>
+        <v>-1.873725487724137</v>
       </c>
       <c r="D59">
-        <v>38.27287005556137</v>
+        <v>37.94243451227587</v>
       </c>
       <c r="E59">
-        <v>38.75064000000001</v>
+        <v>39.44016000000001</v>
       </c>
       <c r="F59">
-        <v>39.30264000000001</v>
+        <v>39.99216000000001</v>
       </c>
       <c r="G59">
         <v>0.176</v>
@@ -6125,37 +6125,37 @@
         <v>2.1</v>
       </c>
       <c r="M59">
-        <v>9.267562512000003</v>
+        <v>9.430151328000003</v>
       </c>
       <c r="N59">
-        <v>-7.167562512000003</v>
+        <v>-7.330151328000003</v>
       </c>
       <c r="O59">
-        <v>-1.791890628000001</v>
+        <v>-1.832537832000001</v>
       </c>
       <c r="P59">
-        <v>-5.375671884000003</v>
+        <v>-5.497613496000002</v>
       </c>
       <c r="Q59">
-        <v>-5.845671884000003</v>
+        <v>-5.967613496000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3190150896597158</v>
+        <v>0.3255202108420899</v>
       </c>
       <c r="T59">
-        <v>2.64219873049257</v>
+        <v>2.705108224075726</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0566491997567008</v>
+        <v>0.05567248941606803</v>
       </c>
       <c r="W59">
-        <v>0.22244211869737</v>
+        <v>0.2226724269956911</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2265967990268032</v>
+        <v>0.222689957664272</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2658684962111786</v>
+        <v>0.2677684962111786</v>
       </c>
       <c r="C60">
-        <v>-1.87372548772413</v>
+        <v>-2.88802412434984</v>
       </c>
       <c r="D60">
-        <v>37.94243451227587</v>
+        <v>37.61765587565016</v>
       </c>
       <c r="E60">
-        <v>39.44016000000001</v>
+        <v>40.12968000000001</v>
       </c>
       <c r="F60">
-        <v>39.99216000000001</v>
+        <v>40.68168000000001</v>
       </c>
       <c r="G60">
         <v>0.176</v>
@@ -6207,37 +6207,37 @@
         <v>2.1</v>
       </c>
       <c r="M60">
-        <v>9.430151328000001</v>
+        <v>9.592740144000002</v>
       </c>
       <c r="N60">
-        <v>-7.330151328000001</v>
+        <v>-7.492740144000003</v>
       </c>
       <c r="O60">
-        <v>-1.832537832</v>
+        <v>-1.873185036000001</v>
       </c>
       <c r="P60">
-        <v>-5.497613496000001</v>
+        <v>-5.619555108000002</v>
       </c>
       <c r="Q60">
-        <v>-5.967613496000002</v>
+        <v>-6.089555108000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3255202108420898</v>
+        <v>0.3323426550089701</v>
       </c>
       <c r="T60">
-        <v>2.705108224075726</v>
+        <v>2.771086473443426</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05567248941606804</v>
+        <v>0.05472888790054146</v>
       </c>
       <c r="W60">
-        <v>0.2226724269956911</v>
+        <v>0.2228949282330523</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2226899576642721</v>
+        <v>0.2189155516021658</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2677684962111786</v>
+        <v>0.2696684962111786</v>
       </c>
       <c r="C61">
-        <v>-2.88802412434984</v>
+        <v>-3.89680988694429</v>
       </c>
       <c r="D61">
-        <v>37.61765587565016</v>
+        <v>37.29839011305572</v>
       </c>
       <c r="E61">
-        <v>40.12968000000001</v>
+        <v>40.81920000000001</v>
       </c>
       <c r="F61">
-        <v>40.68168000000001</v>
+        <v>41.37120000000001</v>
       </c>
       <c r="G61">
         <v>0.176</v>
@@ -6289,37 +6289,37 @@
         <v>2.1</v>
       </c>
       <c r="M61">
-        <v>9.592740144000002</v>
+        <v>9.755328960000002</v>
       </c>
       <c r="N61">
-        <v>-7.492740144000003</v>
+        <v>-7.655328960000002</v>
       </c>
       <c r="O61">
-        <v>-1.873185036000001</v>
+        <v>-1.913832240000001</v>
       </c>
       <c r="P61">
-        <v>-5.619555108000002</v>
+        <v>-5.741496720000002</v>
       </c>
       <c r="Q61">
-        <v>-6.089555108000003</v>
+        <v>-6.211496720000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3323426550089701</v>
+        <v>0.3395062213841943</v>
       </c>
       <c r="T61">
-        <v>2.771086473443426</v>
+        <v>2.840363635279512</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05472888790054146</v>
+        <v>0.05381673976886577</v>
       </c>
       <c r="W61">
-        <v>0.2228949282330523</v>
+        <v>0.2231100127625014</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2189155516021658</v>
+        <v>0.215266959075463</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2696684962111786</v>
+        <v>0.2715684962111786</v>
       </c>
       <c r="C62">
-        <v>-3.89680988694429</v>
+        <v>-4.900221959594312</v>
       </c>
       <c r="D62">
-        <v>37.29839011305572</v>
+        <v>36.98449804040569</v>
       </c>
       <c r="E62">
-        <v>40.81920000000001</v>
+        <v>41.50872</v>
       </c>
       <c r="F62">
-        <v>41.37120000000001</v>
+        <v>42.06072</v>
       </c>
       <c r="G62">
         <v>0.176</v>
@@ -6371,37 +6371,37 @@
         <v>2.1</v>
       </c>
       <c r="M62">
-        <v>9.755328960000002</v>
+        <v>9.917917776000001</v>
       </c>
       <c r="N62">
-        <v>-7.655328960000002</v>
+        <v>-7.817917776000002</v>
       </c>
       <c r="O62">
-        <v>-1.913832240000001</v>
+        <v>-1.954479444</v>
       </c>
       <c r="P62">
-        <v>-5.741496720000002</v>
+        <v>-5.863438332000001</v>
       </c>
       <c r="Q62">
-        <v>-6.211496720000001</v>
+        <v>-6.333438332000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3395062213841943</v>
+        <v>0.3470371501376352</v>
       </c>
       <c r="T62">
-        <v>2.840363635279512</v>
+        <v>2.91319347208155</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05381673976886577</v>
+        <v>0.0529344981333106</v>
       </c>
       <c r="W62">
-        <v>0.2231100127625014</v>
+        <v>0.2233180453401654</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.215266959075463</v>
+        <v>0.2117379925332423</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2715684962111786</v>
+        <v>0.2734684962111786</v>
       </c>
       <c r="C63">
-        <v>-4.900221959594312</v>
+        <v>-5.898394880161732</v>
       </c>
       <c r="D63">
-        <v>36.98449804040569</v>
+        <v>36.67584511983827</v>
       </c>
       <c r="E63">
-        <v>41.50872</v>
+        <v>42.19824000000001</v>
       </c>
       <c r="F63">
-        <v>42.06072</v>
+        <v>42.75024000000001</v>
       </c>
       <c r="G63">
         <v>0.176</v>
@@ -6453,37 +6453,37 @@
         <v>2.1</v>
       </c>
       <c r="M63">
-        <v>9.917917776000001</v>
+        <v>10.080506592</v>
       </c>
       <c r="N63">
-        <v>-7.817917776000002</v>
+        <v>-7.980506592000001</v>
       </c>
       <c r="O63">
-        <v>-1.954479444</v>
+        <v>-1.995126648</v>
       </c>
       <c r="P63">
-        <v>-5.863438332000001</v>
+        <v>-5.985379944000001</v>
       </c>
       <c r="Q63">
-        <v>-6.333438332000002</v>
+        <v>-6.455379944000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3470371501376352</v>
+        <v>0.3549644435623099</v>
       </c>
       <c r="T63">
-        <v>2.91319347208155</v>
+        <v>2.98985645818896</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0529344981333106</v>
+        <v>0.05208071590535397</v>
       </c>
       <c r="W63">
-        <v>0.2233180453401654</v>
+        <v>0.2235193671895175</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2117379925332423</v>
+        <v>0.2083228636214158</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2734684962111786</v>
+        <v>0.2753684962111786</v>
       </c>
       <c r="C64">
-        <v>-5.898394880161732</v>
+        <v>-6.891458732553346</v>
       </c>
       <c r="D64">
-        <v>36.67584511983827</v>
+        <v>36.37230126744666</v>
       </c>
       <c r="E64">
-        <v>42.19824000000001</v>
+        <v>42.88776000000001</v>
       </c>
       <c r="F64">
-        <v>42.75024000000001</v>
+        <v>43.43976000000001</v>
       </c>
       <c r="G64">
         <v>0.176</v>
@@ -6535,37 +6535,37 @@
         <v>2.1</v>
       </c>
       <c r="M64">
-        <v>10.080506592</v>
+        <v>10.243095408</v>
       </c>
       <c r="N64">
-        <v>-7.980506592000001</v>
+        <v>-8.143095408000002</v>
       </c>
       <c r="O64">
-        <v>-1.995126648</v>
+        <v>-2.035773852000001</v>
       </c>
       <c r="P64">
-        <v>-5.985379944000001</v>
+        <v>-6.107321556000002</v>
       </c>
       <c r="Q64">
-        <v>-6.455379944000001</v>
+        <v>-6.577321556000003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3549644435623099</v>
+        <v>0.3633202393342642</v>
       </c>
       <c r="T64">
-        <v>2.98985645818896</v>
+        <v>3.070663389491364</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05208071590535397</v>
+        <v>0.05125403787511025</v>
       </c>
       <c r="W64">
-        <v>0.2235193671895175</v>
+        <v>0.223714297869049</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2083228636214158</v>
+        <v>0.2050161515004409</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2753684962111786</v>
+        <v>0.2772684962111787</v>
       </c>
       <c r="C65">
-        <v>-6.891458732553346</v>
+        <v>-7.879539329521585</v>
       </c>
       <c r="D65">
-        <v>36.37230126744666</v>
+        <v>36.07374067047842</v>
       </c>
       <c r="E65">
-        <v>42.88776000000001</v>
+        <v>43.57728000000001</v>
       </c>
       <c r="F65">
-        <v>43.43976000000001</v>
+        <v>44.12928000000001</v>
       </c>
       <c r="G65">
         <v>0.176</v>
@@ -6617,37 +6617,37 @@
         <v>2.1</v>
       </c>
       <c r="M65">
-        <v>10.243095408</v>
+        <v>10.405684224</v>
       </c>
       <c r="N65">
-        <v>-8.143095408000002</v>
+        <v>-8.305684224000002</v>
       </c>
       <c r="O65">
-        <v>-2.035773852000001</v>
+        <v>-2.076421056</v>
       </c>
       <c r="P65">
-        <v>-6.107321556000002</v>
+        <v>-6.229263168000001</v>
       </c>
       <c r="Q65">
-        <v>-6.577321556000003</v>
+        <v>-6.699263168000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3633202393342642</v>
+        <v>0.3721402459824382</v>
       </c>
       <c r="T65">
-        <v>3.070663389491364</v>
+        <v>3.155959594755013</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05125403787511025</v>
+        <v>0.05045319353331166</v>
       </c>
       <c r="W65">
-        <v>0.223714297869049</v>
+        <v>0.2239031369648451</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2050161515004409</v>
+        <v>0.2018127741332466</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2772684962111787</v>
+        <v>0.2791684962111787</v>
       </c>
       <c r="C66">
-        <v>-7.879539329521585</v>
+        <v>-8.862758386535212</v>
       </c>
       <c r="D66">
-        <v>36.07374067047842</v>
+        <v>35.7800416134648</v>
       </c>
       <c r="E66">
-        <v>43.57728000000001</v>
+        <v>44.26680000000001</v>
       </c>
       <c r="F66">
-        <v>44.12928000000001</v>
+        <v>44.81880000000001</v>
       </c>
       <c r="G66">
         <v>0.176</v>
@@ -6699,37 +6699,37 @@
         <v>2.1</v>
       </c>
       <c r="M66">
-        <v>10.405684224</v>
+        <v>10.56827304</v>
       </c>
       <c r="N66">
-        <v>-8.305684224000002</v>
+        <v>-8.468273040000003</v>
       </c>
       <c r="O66">
-        <v>-2.076421056</v>
+        <v>-2.117068260000001</v>
       </c>
       <c r="P66">
-        <v>-6.229263168000001</v>
+        <v>-6.351204780000002</v>
       </c>
       <c r="Q66">
-        <v>-6.699263168000002</v>
+        <v>-6.821204780000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3721402459824382</v>
+        <v>0.3814642530105079</v>
       </c>
       <c r="T66">
-        <v>3.155959594755013</v>
+        <v>3.246129868890872</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05045319353331166</v>
+        <v>0.04967699055587609</v>
       </c>
       <c r="W66">
-        <v>0.2239031369648451</v>
+        <v>0.2240861656269244</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2018127741332466</v>
+        <v>0.1987079622235043</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2791684962111787</v>
+        <v>0.2810684962111786</v>
       </c>
       <c r="C67">
-        <v>-8.862758386535212</v>
+        <v>-9.841233687225198</v>
       </c>
       <c r="D67">
-        <v>35.7800416134648</v>
+        <v>35.49108631277481</v>
       </c>
       <c r="E67">
-        <v>44.26680000000001</v>
+        <v>44.95632000000001</v>
       </c>
       <c r="F67">
-        <v>44.81880000000001</v>
+        <v>45.50832000000001</v>
       </c>
       <c r="G67">
         <v>0.176</v>
@@ -6781,37 +6781,37 @@
         <v>2.1</v>
       </c>
       <c r="M67">
-        <v>10.56827304</v>
+        <v>10.730861856</v>
       </c>
       <c r="N67">
-        <v>-8.468273040000003</v>
+        <v>-8.630861856000003</v>
       </c>
       <c r="O67">
-        <v>-2.117068260000001</v>
+        <v>-2.157715464000001</v>
       </c>
       <c r="P67">
-        <v>-6.351204780000002</v>
+        <v>-6.473146392000002</v>
       </c>
       <c r="Q67">
-        <v>-6.821204780000002</v>
+        <v>-6.943146392000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3814642530105079</v>
+        <v>0.3913367310402287</v>
       </c>
       <c r="T67">
-        <v>3.246129868890872</v>
+        <v>3.341604276799426</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04967699055587609</v>
+        <v>0.04892430888078706</v>
       </c>
       <c r="W67">
-        <v>0.2240861656269244</v>
+        <v>0.2242636479659104</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1987079622235043</v>
+        <v>0.1956972355231482</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2810684962111786</v>
+        <v>0.2829684962111786</v>
       </c>
       <c r="C68">
-        <v>-9.841233687225198</v>
+        <v>-10.81507924087811</v>
       </c>
       <c r="D68">
-        <v>35.49108631277481</v>
+        <v>35.20676075912191</v>
       </c>
       <c r="E68">
-        <v>44.95632000000001</v>
+        <v>45.64584000000001</v>
       </c>
       <c r="F68">
-        <v>45.50832000000001</v>
+        <v>46.19784000000001</v>
       </c>
       <c r="G68">
         <v>0.176</v>
@@ -6863,37 +6863,37 @@
         <v>2.1</v>
       </c>
       <c r="M68">
-        <v>10.730861856</v>
+        <v>10.893450672</v>
       </c>
       <c r="N68">
-        <v>-8.630861856000003</v>
+        <v>-8.793450672000004</v>
       </c>
       <c r="O68">
-        <v>-2.157715464000001</v>
+        <v>-2.198362668000001</v>
       </c>
       <c r="P68">
-        <v>-6.473146392000002</v>
+        <v>-6.595088004000003</v>
       </c>
       <c r="Q68">
-        <v>-6.943146392000003</v>
+        <v>-7.065088004000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3913367310402287</v>
+        <v>0.4018075410717508</v>
       </c>
       <c r="T68">
-        <v>3.341604276799426</v>
+        <v>3.442865012460015</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04892430888078706</v>
+        <v>0.04819409531540217</v>
       </c>
       <c r="W68">
-        <v>0.2242636479659104</v>
+        <v>0.2244358323246282</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1956972355231482</v>
+        <v>0.1927763812616087</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2829684962111786</v>
+        <v>0.2848684962111786</v>
       </c>
       <c r="C69">
-        <v>-10.81507924087811</v>
+        <v>-11.78440543241932</v>
       </c>
       <c r="D69">
-        <v>35.20676075912191</v>
+        <v>34.92695456758069</v>
       </c>
       <c r="E69">
-        <v>45.64584000000001</v>
+        <v>46.33536000000002</v>
       </c>
       <c r="F69">
-        <v>46.19784000000001</v>
+        <v>46.88736000000002</v>
       </c>
       <c r="G69">
         <v>0.176</v>
@@ -6945,37 +6945,37 @@
         <v>2.1</v>
       </c>
       <c r="M69">
-        <v>10.893450672</v>
+        <v>11.056039488</v>
       </c>
       <c r="N69">
-        <v>-8.793450672000004</v>
+        <v>-8.956039488000004</v>
       </c>
       <c r="O69">
-        <v>-2.198362668000001</v>
+        <v>-2.239009872000001</v>
       </c>
       <c r="P69">
-        <v>-6.595088004000003</v>
+        <v>-6.717029616000003</v>
       </c>
       <c r="Q69">
-        <v>-7.065088004000003</v>
+        <v>-7.187029616000004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4018075410717508</v>
+        <v>0.412932776730243</v>
       </c>
       <c r="T69">
-        <v>3.442865012460015</v>
+        <v>3.550454544099391</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04819409531540217</v>
+        <v>0.04748535861958744</v>
       </c>
       <c r="W69">
-        <v>0.2244358323246282</v>
+        <v>0.2246029524375013</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1927763812616087</v>
+        <v>0.1899414344783497</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2848684962111786</v>
+        <v>0.2867684962111786</v>
       </c>
       <c r="C70">
-        <v>-11.78440543241932</v>
+        <v>-12.74931916530066</v>
       </c>
       <c r="D70">
-        <v>34.92695456758069</v>
+        <v>34.65156083469935</v>
       </c>
       <c r="E70">
-        <v>46.33536000000002</v>
+        <v>47.02488000000001</v>
       </c>
       <c r="F70">
-        <v>46.88736000000002</v>
+        <v>47.57688000000001</v>
       </c>
       <c r="G70">
         <v>0.176</v>
@@ -7027,37 +7027,37 @@
         <v>2.1</v>
       </c>
       <c r="M70">
-        <v>11.056039488</v>
+        <v>11.218628304</v>
       </c>
       <c r="N70">
-        <v>-8.956039488000004</v>
+        <v>-9.118628304000003</v>
       </c>
       <c r="O70">
-        <v>-2.239009872000001</v>
+        <v>-2.279657076000001</v>
       </c>
       <c r="P70">
-        <v>-6.717029616000003</v>
+        <v>-6.838971228000002</v>
       </c>
       <c r="Q70">
-        <v>-7.187029616000004</v>
+        <v>-7.308971228000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.412932776730243</v>
+        <v>0.4247757695279928</v>
       </c>
       <c r="T70">
-        <v>3.550454544099391</v>
+        <v>3.664985335844532</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04748535861958744</v>
+        <v>0.04679716501640501</v>
       </c>
       <c r="W70">
-        <v>0.2246029524375013</v>
+        <v>0.2247652284891317</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1899414344783497</v>
+        <v>0.18718866006562</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2867684962111786</v>
+        <v>0.2886684962111786</v>
       </c>
       <c r="C71">
-        <v>-12.74931916530066</v>
+        <v>-13.70992399768124</v>
       </c>
       <c r="D71">
-        <v>34.65156083469935</v>
+        <v>34.38047600231877</v>
       </c>
       <c r="E71">
-        <v>47.02488000000001</v>
+        <v>47.71440000000001</v>
       </c>
       <c r="F71">
-        <v>47.57688000000001</v>
+        <v>48.26640000000001</v>
       </c>
       <c r="G71">
         <v>0.176</v>
@@ -7109,37 +7109,37 @@
         <v>2.1</v>
       </c>
       <c r="M71">
-        <v>11.218628304</v>
+        <v>11.38121712</v>
       </c>
       <c r="N71">
-        <v>-9.118628304000003</v>
+        <v>-9.281217120000003</v>
       </c>
       <c r="O71">
-        <v>-2.279657076000001</v>
+        <v>-2.320304280000001</v>
       </c>
       <c r="P71">
-        <v>-6.838971228000002</v>
+        <v>-6.960912840000002</v>
       </c>
       <c r="Q71">
-        <v>-7.308971228000003</v>
+        <v>-7.430912840000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4247757695279928</v>
+        <v>0.4374082951789259</v>
       </c>
       <c r="T71">
-        <v>3.664985335844532</v>
+        <v>3.787151513706017</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04679716501640501</v>
+        <v>0.04612863408759923</v>
       </c>
       <c r="W71">
-        <v>0.2247652284891317</v>
+        <v>0.2249228680821441</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.18718866006562</v>
+        <v>0.1845145363503968</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2886684962111786</v>
+        <v>0.2905684962111786</v>
       </c>
       <c r="C72">
-        <v>-13.70992399768124</v>
+        <v>-14.6663202722654</v>
       </c>
       <c r="D72">
-        <v>34.38047600231877</v>
+        <v>34.11359972773461</v>
       </c>
       <c r="E72">
-        <v>47.71440000000001</v>
+        <v>48.40392000000001</v>
       </c>
       <c r="F72">
-        <v>48.26640000000001</v>
+        <v>48.95592000000001</v>
       </c>
       <c r="G72">
         <v>0.176</v>
@@ -7191,37 +7191,37 @@
         <v>2.1</v>
       </c>
       <c r="M72">
-        <v>11.38121712</v>
+        <v>11.543805936</v>
       </c>
       <c r="N72">
-        <v>-9.281217120000003</v>
+        <v>-9.443805936000004</v>
       </c>
       <c r="O72">
-        <v>-2.320304280000001</v>
+        <v>-2.360951484000001</v>
       </c>
       <c r="P72">
-        <v>-6.960912840000002</v>
+        <v>-7.082854452000003</v>
       </c>
       <c r="Q72">
-        <v>-7.430912840000003</v>
+        <v>-7.552854452000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4374082951789259</v>
+        <v>0.4509120294954406</v>
       </c>
       <c r="T72">
-        <v>3.787151513706017</v>
+        <v>3.917742945213122</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04612863408759923</v>
+        <v>0.0454789350159429</v>
       </c>
       <c r="W72">
-        <v>0.2249228680821441</v>
+        <v>0.2250760671232407</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1845145363503968</v>
+        <v>0.1819157400637715</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2905684962111786</v>
+        <v>0.2924684962111787</v>
       </c>
       <c r="C73">
-        <v>-14.66632027226539</v>
+        <v>-15.61860524014035</v>
       </c>
       <c r="D73">
-        <v>34.11359972773461</v>
+        <v>33.85083475985965</v>
       </c>
       <c r="E73">
-        <v>48.40392000000001</v>
+        <v>49.09344000000001</v>
       </c>
       <c r="F73">
-        <v>48.95592000000001</v>
+        <v>49.64544000000001</v>
       </c>
       <c r="G73">
         <v>0.176</v>
@@ -7273,37 +7273,37 @@
         <v>2.1</v>
       </c>
       <c r="M73">
-        <v>11.543805936</v>
+        <v>11.706394752</v>
       </c>
       <c r="N73">
-        <v>-9.443805936000002</v>
+        <v>-9.606394752000003</v>
       </c>
       <c r="O73">
-        <v>-2.360951484000001</v>
+        <v>-2.401598688000001</v>
       </c>
       <c r="P73">
-        <v>-7.082854452000001</v>
+        <v>-7.204796064000003</v>
       </c>
       <c r="Q73">
-        <v>-7.552854452000002</v>
+        <v>-7.674796064000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4509120294954405</v>
+        <v>0.4653803162631348</v>
       </c>
       <c r="T73">
-        <v>3.91774294521312</v>
+        <v>4.057662336113588</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0454789350159429</v>
+        <v>0.04484728314072147</v>
       </c>
       <c r="W73">
-        <v>0.2250760671232407</v>
+        <v>0.2252250106354179</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1819157400637715</v>
+        <v>0.1793891325628858</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2924684962111787</v>
+        <v>0.2943684962111786</v>
       </c>
       <c r="C74">
-        <v>-15.61860524014035</v>
+        <v>-16.56687317893422</v>
       </c>
       <c r="D74">
-        <v>33.85083475985965</v>
+        <v>33.59208682106579</v>
       </c>
       <c r="E74">
-        <v>49.09344000000001</v>
+        <v>49.78296000000001</v>
       </c>
       <c r="F74">
-        <v>49.64544000000001</v>
+        <v>50.33496000000001</v>
       </c>
       <c r="G74">
         <v>0.176</v>
@@ -7355,37 +7355,37 @@
         <v>2.1</v>
       </c>
       <c r="M74">
-        <v>11.706394752</v>
+        <v>11.868983568</v>
       </c>
       <c r="N74">
-        <v>-9.606394752000003</v>
+        <v>-9.768983568000003</v>
       </c>
       <c r="O74">
-        <v>-2.401598688000001</v>
+        <v>-2.442245892000001</v>
       </c>
       <c r="P74">
-        <v>-7.204796064000003</v>
+        <v>-7.326737676000002</v>
       </c>
       <c r="Q74">
-        <v>-7.674796064000002</v>
+        <v>-7.796737676000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4653803162631348</v>
+        <v>0.4809203279765842</v>
       </c>
       <c r="T74">
-        <v>4.057662336113588</v>
+        <v>4.207946126340017</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04484728314072147</v>
+        <v>0.04423293679632802</v>
       </c>
       <c r="W74">
-        <v>0.2252250106354179</v>
+        <v>0.2253698735034259</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1793891325628858</v>
+        <v>0.176931747185312</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2943684962111786</v>
+        <v>0.2962684962111786</v>
       </c>
       <c r="C75">
-        <v>-16.56687317893422</v>
+        <v>-17.51121550559606</v>
       </c>
       <c r="D75">
-        <v>33.59208682106579</v>
+        <v>33.33726449440395</v>
       </c>
       <c r="E75">
-        <v>49.78296000000001</v>
+        <v>50.47248000000001</v>
       </c>
       <c r="F75">
-        <v>50.33496000000001</v>
+        <v>51.02448000000001</v>
       </c>
       <c r="G75">
         <v>0.176</v>
@@ -7437,37 +7437,37 @@
         <v>2.1</v>
       </c>
       <c r="M75">
-        <v>11.868983568</v>
+        <v>12.031572384</v>
       </c>
       <c r="N75">
-        <v>-9.768983568000003</v>
+        <v>-9.931572384000004</v>
       </c>
       <c r="O75">
-        <v>-2.442245892000001</v>
+        <v>-2.482893096000001</v>
       </c>
       <c r="P75">
-        <v>-7.326737676000002</v>
+        <v>-7.448679288000003</v>
       </c>
       <c r="Q75">
-        <v>-7.796737676000003</v>
+        <v>-7.918679288000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4809203279765842</v>
+        <v>0.4976557252064528</v>
       </c>
       <c r="T75">
-        <v>4.207946126340017</v>
+        <v>4.369790208122326</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04423293679632802</v>
+        <v>0.04363519440718845</v>
       </c>
       <c r="W75">
-        <v>0.2253698735034259</v>
+        <v>0.225510821158785</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.176931747185312</v>
+        <v>0.1745407776287538</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2962684962111786</v>
+        <v>0.2981684962111786</v>
       </c>
       <c r="C76">
-        <v>-17.51121550559606</v>
+        <v>-18.45172088408152</v>
       </c>
       <c r="D76">
-        <v>33.33726449440395</v>
+        <v>33.08627911591849</v>
       </c>
       <c r="E76">
-        <v>50.47248000000001</v>
+        <v>51.16200000000001</v>
       </c>
       <c r="F76">
-        <v>51.02448000000001</v>
+        <v>51.71400000000001</v>
       </c>
       <c r="G76">
         <v>0.176</v>
@@ -7519,37 +7519,37 @@
         <v>2.1</v>
       </c>
       <c r="M76">
-        <v>12.031572384</v>
+        <v>12.1941612</v>
       </c>
       <c r="N76">
-        <v>-9.931572384000004</v>
+        <v>-10.0941612</v>
       </c>
       <c r="O76">
-        <v>-2.482893096000001</v>
+        <v>-2.523540300000001</v>
       </c>
       <c r="P76">
-        <v>-7.448679288000003</v>
+        <v>-7.570620900000003</v>
       </c>
       <c r="Q76">
-        <v>-7.918679288000003</v>
+        <v>-8.040620900000004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4976557252064528</v>
+        <v>0.515729954214711</v>
       </c>
       <c r="T76">
-        <v>4.369790208122326</v>
+        <v>4.54458181644722</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04363519440718845</v>
+        <v>0.04305339181509261</v>
       </c>
       <c r="W76">
-        <v>0.225510821158785</v>
+        <v>0.2256480102100012</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1745407776287538</v>
+        <v>0.1722135672603704</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2981684962111786</v>
+        <v>0.3000684962111786</v>
       </c>
       <c r="C77">
-        <v>-18.45172088408152</v>
+        <v>-19.38847532821035</v>
       </c>
       <c r="D77">
-        <v>33.08627911591849</v>
+        <v>32.83904467178966</v>
       </c>
       <c r="E77">
-        <v>51.16200000000001</v>
+        <v>51.85152000000001</v>
       </c>
       <c r="F77">
-        <v>51.71400000000001</v>
+        <v>52.40352000000001</v>
       </c>
       <c r="G77">
         <v>0.176</v>
@@ -7601,37 +7601,37 @@
         <v>2.1</v>
       </c>
       <c r="M77">
-        <v>12.1941612</v>
+        <v>12.356750016</v>
       </c>
       <c r="N77">
-        <v>-10.0941612</v>
+        <v>-10.256750016</v>
       </c>
       <c r="O77">
-        <v>-2.523540300000001</v>
+        <v>-2.564187504000001</v>
       </c>
       <c r="P77">
-        <v>-7.570620900000003</v>
+        <v>-7.692562512000002</v>
       </c>
       <c r="Q77">
-        <v>-8.040620900000004</v>
+        <v>-8.162562512000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.515729954214711</v>
+        <v>0.5353103689736572</v>
       </c>
       <c r="T77">
-        <v>4.54458181644722</v>
+        <v>4.733939392132521</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04305339181509261</v>
+        <v>0.0424868998175256</v>
       </c>
       <c r="W77">
-        <v>0.2256480102100012</v>
+        <v>0.2257815890230275</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1722135672603704</v>
+        <v>0.1699475992701024</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3000684962111786</v>
+        <v>0.3019684962111786</v>
       </c>
       <c r="C78">
-        <v>-19.38847532821035</v>
+        <v>-20.32156229994666</v>
       </c>
       <c r="D78">
-        <v>32.83904467178966</v>
+        <v>32.59547770005335</v>
       </c>
       <c r="E78">
-        <v>51.85152000000001</v>
+        <v>52.54104000000001</v>
       </c>
       <c r="F78">
-        <v>52.40352000000001</v>
+        <v>53.09304000000001</v>
       </c>
       <c r="G78">
         <v>0.176</v>
@@ -7683,37 +7683,37 @@
         <v>2.1</v>
       </c>
       <c r="M78">
-        <v>12.356750016</v>
+        <v>12.519338832</v>
       </c>
       <c r="N78">
-        <v>-10.256750016</v>
+        <v>-10.419338832</v>
       </c>
       <c r="O78">
-        <v>-2.564187504000001</v>
+        <v>-2.604834708000001</v>
       </c>
       <c r="P78">
-        <v>-7.692562512000002</v>
+        <v>-7.814504124000003</v>
       </c>
       <c r="Q78">
-        <v>-8.162562512000003</v>
+        <v>-8.284504124000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5353103689736572</v>
+        <v>0.556593428494251</v>
       </c>
       <c r="T78">
-        <v>4.733939392132521</v>
+        <v>4.939762843964369</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0424868998175256</v>
+        <v>0.04193512189781748</v>
       </c>
       <c r="W78">
-        <v>0.2257815890230275</v>
+        <v>0.2259116982564947</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1699475992701024</v>
+        <v>0.1677404875912699</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3019684962111786</v>
+        <v>0.3038684962111786</v>
       </c>
       <c r="C79">
-        <v>-20.32156229994666</v>
+        <v>-21.2510628033376</v>
       </c>
       <c r="D79">
-        <v>32.59547770005335</v>
+        <v>32.35549719666241</v>
       </c>
       <c r="E79">
-        <v>52.54104000000001</v>
+        <v>53.23056000000001</v>
       </c>
       <c r="F79">
-        <v>53.09304000000001</v>
+        <v>53.78256000000001</v>
       </c>
       <c r="G79">
         <v>0.176</v>
@@ -7765,37 +7765,37 @@
         <v>2.1</v>
       </c>
       <c r="M79">
-        <v>12.519338832</v>
+        <v>12.681927648</v>
       </c>
       <c r="N79">
-        <v>-10.419338832</v>
+        <v>-10.581927648</v>
       </c>
       <c r="O79">
-        <v>-2.604834708000001</v>
+        <v>-2.645481912000001</v>
       </c>
       <c r="P79">
-        <v>-7.814504124000003</v>
+        <v>-7.936445736000003</v>
       </c>
       <c r="Q79">
-        <v>-8.284504124000003</v>
+        <v>-8.406445736000004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.556593428494251</v>
+        <v>0.5798113116076261</v>
       </c>
       <c r="T79">
-        <v>4.939762843964369</v>
+        <v>5.164297518690023</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04193512189781748</v>
+        <v>0.04139749212989674</v>
       </c>
       <c r="W79">
-        <v>0.2259116982564947</v>
+        <v>0.2260384713557703</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1677404875912699</v>
+        <v>0.165589968519587</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3038684962111786</v>
+        <v>0.3057684962111786</v>
       </c>
       <c r="C80">
-        <v>-21.2510628033376</v>
+        <v>-22.17705547433278</v>
       </c>
       <c r="D80">
-        <v>32.35549719666241</v>
+        <v>32.11902452566723</v>
       </c>
       <c r="E80">
-        <v>53.23056000000001</v>
+        <v>53.92008000000001</v>
       </c>
       <c r="F80">
-        <v>53.78256000000001</v>
+        <v>54.47208000000001</v>
       </c>
       <c r="G80">
         <v>0.176</v>
@@ -7847,37 +7847,37 @@
         <v>2.1</v>
       </c>
       <c r="M80">
-        <v>12.681927648</v>
+        <v>12.844516464</v>
       </c>
       <c r="N80">
-        <v>-10.581927648</v>
+        <v>-10.744516464</v>
       </c>
       <c r="O80">
-        <v>-2.645481912000001</v>
+        <v>-2.686129116000001</v>
       </c>
       <c r="P80">
-        <v>-7.936445736000003</v>
+        <v>-8.058387348000004</v>
       </c>
       <c r="Q80">
-        <v>-8.406445736000004</v>
+        <v>-8.528387348000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5798113116076261</v>
+        <v>0.6052404216841797</v>
       </c>
       <c r="T80">
-        <v>5.164297518690023</v>
+        <v>5.410216448151452</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04139749212989674</v>
+        <v>0.04087347324217653</v>
       </c>
       <c r="W80">
-        <v>0.2260384713557703</v>
+        <v>0.2261620350094948</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.165589968519587</v>
+        <v>0.1634938929687061</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3057684962111786</v>
+        <v>0.3076684962111786</v>
       </c>
       <c r="C81">
-        <v>-22.17705547433278</v>
+        <v>-23.09961666669352</v>
       </c>
       <c r="D81">
-        <v>32.11902452566723</v>
+        <v>31.88598333330649</v>
       </c>
       <c r="E81">
-        <v>53.92008000000001</v>
+        <v>54.60960000000001</v>
       </c>
       <c r="F81">
-        <v>54.47208000000001</v>
+        <v>55.16160000000001</v>
       </c>
       <c r="G81">
         <v>0.176</v>
@@ -7929,37 +7929,37 @@
         <v>2.1</v>
       </c>
       <c r="M81">
-        <v>12.844516464</v>
+        <v>13.00710528</v>
       </c>
       <c r="N81">
-        <v>-10.744516464</v>
+        <v>-10.90710528000001</v>
       </c>
       <c r="O81">
-        <v>-2.686129116000001</v>
+        <v>-2.726776320000001</v>
       </c>
       <c r="P81">
-        <v>-8.058387348000004</v>
+        <v>-8.180328960000004</v>
       </c>
       <c r="Q81">
-        <v>-8.528387348000004</v>
+        <v>-8.650328960000005</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6052404216841797</v>
+        <v>0.6332124427683887</v>
       </c>
       <c r="T81">
-        <v>5.410216448151452</v>
+        <v>5.680727270559025</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04087347324217653</v>
+        <v>0.04036255482664932</v>
       </c>
       <c r="W81">
-        <v>0.2261620350094948</v>
+        <v>0.2262825095718761</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1634938929687061</v>
+        <v>0.1614502193065972</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3076684962111786</v>
+        <v>0.3095684962111785</v>
       </c>
       <c r="C82">
-        <v>-23.09961666669352</v>
+        <v>-24.01882053418912</v>
       </c>
       <c r="D82">
-        <v>31.88598333330649</v>
+        <v>31.6562994658109</v>
       </c>
       <c r="E82">
-        <v>54.60960000000001</v>
+        <v>55.29912000000002</v>
       </c>
       <c r="F82">
-        <v>55.16160000000001</v>
+        <v>55.85112000000002</v>
       </c>
       <c r="G82">
         <v>0.176</v>
@@ -8011,37 +8011,37 @@
         <v>2.1</v>
       </c>
       <c r="M82">
-        <v>13.00710528</v>
+        <v>13.169694096</v>
       </c>
       <c r="N82">
-        <v>-10.90710528000001</v>
+        <v>-11.069694096</v>
       </c>
       <c r="O82">
-        <v>-2.726776320000001</v>
+        <v>-2.767423524000001</v>
       </c>
       <c r="P82">
-        <v>-8.180328960000004</v>
+        <v>-8.302270572000003</v>
       </c>
       <c r="Q82">
-        <v>-8.650328960000005</v>
+        <v>-8.772270572000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6332124427683887</v>
+        <v>0.6641288871246197</v>
       </c>
       <c r="T82">
-        <v>5.680727270559025</v>
+        <v>5.979712916377921</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04036255482664932</v>
+        <v>0.0398642516806413</v>
       </c>
       <c r="W82">
-        <v>0.2262825095718761</v>
+        <v>0.2264000094537048</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1614502193065972</v>
+        <v>0.1594570067225651</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3095684962111785</v>
+        <v>0.3114684962111787</v>
       </c>
       <c r="C83">
-        <v>-24.01882053418912</v>
+        <v>-24.93473910926607</v>
       </c>
       <c r="D83">
-        <v>31.6562994658109</v>
+        <v>31.42990089073395</v>
       </c>
       <c r="E83">
-        <v>55.29912000000002</v>
+        <v>55.98864000000002</v>
       </c>
       <c r="F83">
-        <v>55.85112000000002</v>
+        <v>56.54064000000002</v>
       </c>
       <c r="G83">
         <v>0.176</v>
@@ -8093,37 +8093,37 @@
         <v>2.1</v>
       </c>
       <c r="M83">
-        <v>13.169694096</v>
+        <v>13.33228291200001</v>
       </c>
       <c r="N83">
-        <v>-11.069694096</v>
+        <v>-11.23228291200001</v>
       </c>
       <c r="O83">
-        <v>-2.767423524000001</v>
+        <v>-2.808070728000001</v>
       </c>
       <c r="P83">
-        <v>-8.302270572000003</v>
+        <v>-8.424212184000005</v>
       </c>
       <c r="Q83">
-        <v>-8.772270572000004</v>
+        <v>-8.894212184000006</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6641288871246197</v>
+        <v>0.6984804919648766</v>
       </c>
       <c r="T83">
-        <v>5.979712916377921</v>
+        <v>6.31191918951003</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0398642516806413</v>
+        <v>0.03937810226990177</v>
       </c>
       <c r="W83">
-        <v>0.2264000094537048</v>
+        <v>0.2265146434847572</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1594570067225651</v>
+        <v>0.1575124090796071</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3114684962111787</v>
+        <v>0.3133684962111786</v>
       </c>
       <c r="C84">
-        <v>-24.93473910926607</v>
+        <v>-25.84744237836535</v>
       </c>
       <c r="D84">
-        <v>31.42990089073395</v>
+        <v>31.20671762163466</v>
       </c>
       <c r="E84">
-        <v>55.98864000000002</v>
+        <v>56.67816000000001</v>
       </c>
       <c r="F84">
-        <v>56.54064000000002</v>
+        <v>57.23016000000001</v>
       </c>
       <c r="G84">
         <v>0.176</v>
@@ -8175,37 +8175,37 @@
         <v>2.1</v>
       </c>
       <c r="M84">
-        <v>13.33228291200001</v>
+        <v>13.494871728</v>
       </c>
       <c r="N84">
-        <v>-11.23228291200001</v>
+        <v>-11.394871728</v>
       </c>
       <c r="O84">
-        <v>-2.808070728000001</v>
+        <v>-2.848717932000001</v>
       </c>
       <c r="P84">
-        <v>-8.424212184000005</v>
+        <v>-8.546153796000002</v>
       </c>
       <c r="Q84">
-        <v>-8.894212184000006</v>
+        <v>-9.016153796000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6984804919648766</v>
+        <v>0.7368734620804576</v>
       </c>
       <c r="T84">
-        <v>6.31191918951003</v>
+        <v>6.683208553598855</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03937810226990177</v>
+        <v>0.03890366730279453</v>
       </c>
       <c r="W84">
-        <v>0.2265146434847572</v>
+        <v>0.2266265152500011</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1575124090796071</v>
+        <v>0.1556146692111781</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3133684962111786</v>
+        <v>0.3152684962111786</v>
       </c>
       <c r="C85">
-        <v>-25.84744237836535</v>
+        <v>-26.75699835405372</v>
       </c>
       <c r="D85">
-        <v>31.20671762163466</v>
+        <v>30.98668164594629</v>
       </c>
       <c r="E85">
-        <v>56.67816000000001</v>
+        <v>57.36768000000001</v>
       </c>
       <c r="F85">
-        <v>57.23016000000001</v>
+        <v>57.91968000000001</v>
       </c>
       <c r="G85">
         <v>0.176</v>
@@ -8257,37 +8257,37 @@
         <v>2.1</v>
       </c>
       <c r="M85">
-        <v>13.494871728</v>
+        <v>13.657460544</v>
       </c>
       <c r="N85">
-        <v>-11.394871728</v>
+        <v>-11.557460544</v>
       </c>
       <c r="O85">
-        <v>-2.848717932000001</v>
+        <v>-2.889365136000001</v>
       </c>
       <c r="P85">
-        <v>-8.546153796000002</v>
+        <v>-8.668095408000003</v>
       </c>
       <c r="Q85">
-        <v>-9.016153796000003</v>
+        <v>-9.138095408000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7368734620804576</v>
+        <v>0.7800655534604862</v>
       </c>
       <c r="T85">
-        <v>6.683208553598855</v>
+        <v>7.100909088198784</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03890366730279453</v>
+        <v>0.03844052840633268</v>
       </c>
       <c r="W85">
-        <v>0.2266265152500011</v>
+        <v>0.2267357234017867</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1556146692111781</v>
+        <v>0.1537621136253307</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3152684962111786</v>
+        <v>0.3171684962111786</v>
       </c>
       <c r="C86">
-        <v>-26.75699835405372</v>
+        <v>-27.66347314412443</v>
       </c>
       <c r="D86">
-        <v>30.98668164594629</v>
+        <v>30.76972685587558</v>
       </c>
       <c r="E86">
-        <v>57.36768000000001</v>
+        <v>58.05720000000001</v>
       </c>
       <c r="F86">
-        <v>57.91968000000001</v>
+        <v>58.60920000000001</v>
       </c>
       <c r="G86">
         <v>0.176</v>
@@ -8339,37 +8339,37 @@
         <v>2.1</v>
       </c>
       <c r="M86">
-        <v>13.657460544</v>
+        <v>13.82004936</v>
       </c>
       <c r="N86">
-        <v>-11.557460544</v>
+        <v>-11.72004936</v>
       </c>
       <c r="O86">
-        <v>-2.889365136000001</v>
+        <v>-2.930012340000001</v>
       </c>
       <c r="P86">
-        <v>-8.668095408000003</v>
+        <v>-8.790037020000002</v>
       </c>
       <c r="Q86">
-        <v>-9.138095408000003</v>
+        <v>-9.260037020000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7800655534604858</v>
+        <v>0.8290165903578515</v>
       </c>
       <c r="T86">
-        <v>7.10090908819878</v>
+        <v>7.574303027412031</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03844052840633269</v>
+        <v>0.03798828689566995</v>
       </c>
       <c r="W86">
-        <v>0.2267357234017867</v>
+        <v>0.226842361950001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1537621136253308</v>
+        <v>0.1519531475826797</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3171684962111786</v>
+        <v>0.3190684962111786</v>
       </c>
       <c r="C87">
-        <v>-27.66347314412443</v>
+        <v>-28.56693101781546</v>
       </c>
       <c r="D87">
-        <v>30.76972685587558</v>
+        <v>30.55578898218456</v>
       </c>
       <c r="E87">
-        <v>58.05720000000001</v>
+        <v>58.74672000000001</v>
       </c>
       <c r="F87">
-        <v>58.60920000000001</v>
+        <v>59.29872000000001</v>
       </c>
       <c r="G87">
         <v>0.176</v>
@@ -8421,37 +8421,37 @@
         <v>2.1</v>
       </c>
       <c r="M87">
-        <v>13.82004936</v>
+        <v>13.982638176</v>
       </c>
       <c r="N87">
-        <v>-11.72004936</v>
+        <v>-11.882638176</v>
       </c>
       <c r="O87">
-        <v>-2.930012340000001</v>
+        <v>-2.970659544000001</v>
       </c>
       <c r="P87">
-        <v>-8.790037020000002</v>
+        <v>-8.911978632000004</v>
       </c>
       <c r="Q87">
-        <v>-9.260037020000002</v>
+        <v>-9.381978632000004</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8290165903578515</v>
+        <v>0.8849606325262694</v>
       </c>
       <c r="T87">
-        <v>7.574303027412031</v>
+        <v>8.115324672227176</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03798828689566995</v>
+        <v>0.03754656262944123</v>
       </c>
       <c r="W87">
-        <v>0.226842361950001</v>
+        <v>0.2269465205319778</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1519531475826797</v>
+        <v>0.1501862505177649</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3190684962111786</v>
+        <v>0.3209684962111786</v>
       </c>
       <c r="C88">
-        <v>-28.56693101781546</v>
+        <v>-29.46743446928439</v>
       </c>
       <c r="D88">
-        <v>30.55578898218456</v>
+        <v>30.34480553071562</v>
       </c>
       <c r="E88">
-        <v>58.74672000000001</v>
+        <v>59.43624000000001</v>
       </c>
       <c r="F88">
-        <v>59.29872000000001</v>
+        <v>59.98824000000001</v>
       </c>
       <c r="G88">
         <v>0.176</v>
@@ -8503,37 +8503,37 @@
         <v>2.1</v>
       </c>
       <c r="M88">
-        <v>13.982638176</v>
+        <v>14.145226992</v>
       </c>
       <c r="N88">
-        <v>-11.882638176</v>
+        <v>-12.045226992</v>
       </c>
       <c r="O88">
-        <v>-2.970659544000001</v>
+        <v>-3.011306748000001</v>
       </c>
       <c r="P88">
-        <v>-8.911978632000004</v>
+        <v>-9.033920244000003</v>
       </c>
       <c r="Q88">
-        <v>-9.381978632000004</v>
+        <v>-9.503920244000003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8849606325262694</v>
+        <v>0.9495114504129055</v>
       </c>
       <c r="T88">
-        <v>8.115324672227176</v>
+        <v>8.739580416244651</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03754656262944123</v>
+        <v>0.03711499294404536</v>
       </c>
       <c r="W88">
-        <v>0.2269465205319778</v>
+        <v>0.2270482846637941</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1501862505177649</v>
+        <v>0.1484599717761814</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3209684962111786</v>
+        <v>0.3228684962111786</v>
       </c>
       <c r="C89">
-        <v>-29.46743446928439</v>
+        <v>-30.36504427847156</v>
       </c>
       <c r="D89">
-        <v>30.34480553071562</v>
+        <v>30.13671572152845</v>
       </c>
       <c r="E89">
-        <v>59.43624000000001</v>
+        <v>60.12576000000001</v>
       </c>
       <c r="F89">
-        <v>59.98824000000001</v>
+        <v>60.67776000000001</v>
       </c>
       <c r="G89">
         <v>0.176</v>
@@ -8585,37 +8585,37 @@
         <v>2.1</v>
       </c>
       <c r="M89">
-        <v>14.145226992</v>
+        <v>14.307815808</v>
       </c>
       <c r="N89">
-        <v>-12.045226992</v>
+        <v>-12.207815808</v>
       </c>
       <c r="O89">
-        <v>-3.011306748000001</v>
+        <v>-3.051953952000001</v>
       </c>
       <c r="P89">
-        <v>-9.033920244000003</v>
+        <v>-9.155861856000003</v>
       </c>
       <c r="Q89">
-        <v>-9.503920244000003</v>
+        <v>-9.625861856000004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9495114504129055</v>
+        <v>1.024820737947315</v>
       </c>
       <c r="T89">
-        <v>8.739580416244651</v>
+        <v>9.467878784265041</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03711499294404536</v>
+        <v>0.03669323166059029</v>
       </c>
       <c r="W89">
-        <v>0.2270482846637941</v>
+        <v>0.2271477359744328</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1484599717761814</v>
+        <v>0.1467729266423611</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3228684962111786</v>
+        <v>0.3247684962111786</v>
       </c>
       <c r="C90">
-        <v>-30.36504427847156</v>
+        <v>-31.25981956947603</v>
       </c>
       <c r="D90">
-        <v>30.13671572152845</v>
+        <v>29.93146043052398</v>
       </c>
       <c r="E90">
-        <v>60.12576000000001</v>
+        <v>60.81528000000002</v>
       </c>
       <c r="F90">
-        <v>60.67776000000001</v>
+        <v>61.36728000000002</v>
       </c>
       <c r="G90">
         <v>0.176</v>
@@ -8667,37 +8667,37 @@
         <v>2.1</v>
       </c>
       <c r="M90">
-        <v>14.307815808</v>
+        <v>14.470404624</v>
       </c>
       <c r="N90">
-        <v>-12.207815808</v>
+        <v>-12.370404624</v>
       </c>
       <c r="O90">
-        <v>-3.051953952000001</v>
+        <v>-3.092601156000001</v>
       </c>
       <c r="P90">
-        <v>-9.155861856000003</v>
+        <v>-9.277803468000004</v>
       </c>
       <c r="Q90">
-        <v>-9.625861856000004</v>
+        <v>-9.747803468000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.024820737947315</v>
+        <v>1.113822623215252</v>
       </c>
       <c r="T90">
-        <v>9.467878784265041</v>
+        <v>10.32859503738005</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03669323166059029</v>
+        <v>0.03628094815878591</v>
       </c>
       <c r="W90">
-        <v>0.2271477359744328</v>
+        <v>0.2272449524241583</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1467729266423611</v>
+        <v>0.1451237926351436</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3247684962111786</v>
+        <v>0.3266684962111786</v>
       </c>
       <c r="C91">
-        <v>-31.25981956947603</v>
+        <v>-32.1518178665622</v>
       </c>
       <c r="D91">
-        <v>29.93146043052398</v>
+        <v>29.72898213343781</v>
       </c>
       <c r="E91">
-        <v>60.81528000000002</v>
+        <v>61.50480000000001</v>
       </c>
       <c r="F91">
-        <v>61.36728000000002</v>
+        <v>62.05680000000001</v>
       </c>
       <c r="G91">
         <v>0.176</v>
@@ -8749,37 +8749,37 @@
         <v>2.1</v>
       </c>
       <c r="M91">
-        <v>14.470404624</v>
+        <v>14.63299344</v>
       </c>
       <c r="N91">
-        <v>-12.370404624</v>
+        <v>-12.53299344</v>
       </c>
       <c r="O91">
-        <v>-3.092601156000001</v>
+        <v>-3.133248360000001</v>
       </c>
       <c r="P91">
-        <v>-9.277803468000004</v>
+        <v>-9.399745080000002</v>
       </c>
       <c r="Q91">
-        <v>-9.747803468000004</v>
+        <v>-9.869745080000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.113822623215252</v>
+        <v>1.220624885536778</v>
       </c>
       <c r="T91">
-        <v>10.32859503738005</v>
+        <v>11.36145454111805</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03628094815878591</v>
+        <v>0.03587782651257718</v>
       </c>
       <c r="W91">
-        <v>0.2272449524241583</v>
+        <v>0.2273400085083343</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1451237926351436</v>
+        <v>0.1435113060503087</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3266684962111786</v>
+        <v>0.3285684962111787</v>
       </c>
       <c r="C92">
-        <v>-32.1518178665622</v>
+        <v>-33.04109514790853</v>
       </c>
       <c r="D92">
-        <v>29.72898213343781</v>
+        <v>29.52922485209148</v>
       </c>
       <c r="E92">
-        <v>61.50480000000001</v>
+        <v>62.19432000000001</v>
       </c>
       <c r="F92">
-        <v>62.05680000000001</v>
+        <v>62.74632000000001</v>
       </c>
       <c r="G92">
         <v>0.176</v>
@@ -8831,37 +8831,37 @@
         <v>2.1</v>
       </c>
       <c r="M92">
-        <v>14.63299344</v>
+        <v>14.795582256</v>
       </c>
       <c r="N92">
-        <v>-12.53299344</v>
+        <v>-12.695582256</v>
       </c>
       <c r="O92">
-        <v>-3.133248360000001</v>
+        <v>-3.173895564000001</v>
       </c>
       <c r="P92">
-        <v>-9.399745080000002</v>
+        <v>-9.521686692000003</v>
       </c>
       <c r="Q92">
-        <v>-9.869745080000003</v>
+        <v>-9.991686692000004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.220624885536778</v>
+        <v>1.351160983929753</v>
       </c>
       <c r="T92">
-        <v>11.36145454111805</v>
+        <v>12.62383837902006</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03587782651257718</v>
+        <v>0.03548356468276864</v>
       </c>
       <c r="W92">
-        <v>0.2273400085083343</v>
+        <v>0.2274329754478032</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1435113060503087</v>
+        <v>0.1419342587310746</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3285684962111787</v>
+        <v>0.3304684962111786</v>
       </c>
       <c r="C93">
-        <v>-33.04109514790853</v>
+        <v>-33.92770589720364</v>
       </c>
       <c r="D93">
-        <v>29.52922485209148</v>
+        <v>29.33213410279638</v>
       </c>
       <c r="E93">
-        <v>62.19432000000001</v>
+        <v>62.88384000000001</v>
       </c>
       <c r="F93">
-        <v>62.74632000000001</v>
+        <v>63.43584000000001</v>
       </c>
       <c r="G93">
         <v>0.176</v>
@@ -8913,37 +8913,37 @@
         <v>2.1</v>
       </c>
       <c r="M93">
-        <v>14.795582256</v>
+        <v>14.958171072</v>
       </c>
       <c r="N93">
-        <v>-12.695582256</v>
+        <v>-12.858171072</v>
       </c>
       <c r="O93">
-        <v>-3.173895564000001</v>
+        <v>-3.214542768000001</v>
       </c>
       <c r="P93">
-        <v>-9.521686692000003</v>
+        <v>-9.643628304000003</v>
       </c>
       <c r="Q93">
-        <v>-9.991686692000004</v>
+        <v>-10.113628304</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.351160983929753</v>
+        <v>1.514331106920973</v>
       </c>
       <c r="T93">
-        <v>12.62383837902006</v>
+        <v>14.20181817639757</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03548356468276864</v>
+        <v>0.03509787376230376</v>
       </c>
       <c r="W93">
-        <v>0.2274329754478032</v>
+        <v>0.2275239213668488</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1419342587310746</v>
+        <v>0.140391495049215</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3304684962111786</v>
+        <v>0.3323684962111786</v>
       </c>
       <c r="C94">
-        <v>-33.92770589720364</v>
+        <v>-34.81170315319008</v>
       </c>
       <c r="D94">
-        <v>29.33213410279638</v>
+        <v>29.13765684680993</v>
       </c>
       <c r="E94">
-        <v>62.88384000000001</v>
+        <v>63.57336000000002</v>
       </c>
       <c r="F94">
-        <v>63.43584000000001</v>
+        <v>64.12536000000001</v>
       </c>
       <c r="G94">
         <v>0.176</v>
@@ -8995,37 +8995,37 @@
         <v>2.1</v>
       </c>
       <c r="M94">
-        <v>14.958171072</v>
+        <v>15.120759888</v>
       </c>
       <c r="N94">
-        <v>-12.858171072</v>
+        <v>-13.020759888</v>
       </c>
       <c r="O94">
-        <v>-3.214542768000001</v>
+        <v>-3.255189972000001</v>
       </c>
       <c r="P94">
-        <v>-9.643628304000003</v>
+        <v>-9.765569916000004</v>
       </c>
       <c r="Q94">
-        <v>-10.113628304</v>
+        <v>-10.235569916</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.514331106920973</v>
+        <v>1.72412126505254</v>
       </c>
       <c r="T94">
-        <v>14.20181817639757</v>
+        <v>16.23064934445437</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03509787376230376</v>
+        <v>0.03472047727023598</v>
       </c>
       <c r="W94">
-        <v>0.2275239213668488</v>
+        <v>0.2276129114596784</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.140391495049215</v>
+        <v>0.1388819090809439</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3323684962111786</v>
+        <v>0.3342684962111787</v>
       </c>
       <c r="C95">
-        <v>-34.81170315319008</v>
+        <v>-35.69313855725006</v>
       </c>
       <c r="D95">
-        <v>29.13765684680993</v>
+        <v>28.94574144274996</v>
       </c>
       <c r="E95">
-        <v>63.57336000000002</v>
+        <v>64.26288000000001</v>
       </c>
       <c r="F95">
-        <v>64.12536000000001</v>
+        <v>64.81488000000002</v>
       </c>
       <c r="G95">
         <v>0.176</v>
@@ -9077,37 +9077,37 @@
         <v>2.1</v>
       </c>
       <c r="M95">
-        <v>15.120759888</v>
+        <v>15.28334870400001</v>
       </c>
       <c r="N95">
-        <v>-13.020759888</v>
+        <v>-13.18334870400001</v>
       </c>
       <c r="O95">
-        <v>-3.255189972000001</v>
+        <v>-3.295837176000001</v>
       </c>
       <c r="P95">
-        <v>-9.765569916000004</v>
+        <v>-9.887511528000005</v>
       </c>
       <c r="Q95">
-        <v>-10.235569916</v>
+        <v>-10.35751152800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.72412126505254</v>
+        <v>2.003841475894631</v>
       </c>
       <c r="T95">
-        <v>16.23064934445437</v>
+        <v>18.9357575685301</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03472047727023598</v>
+        <v>0.03435111049076538</v>
       </c>
       <c r="W95">
-        <v>0.2276129114596784</v>
+        <v>0.2277000081462776</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1388819090809439</v>
+        <v>0.1374044419630615</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3342684962111787</v>
+        <v>0.3361684962111787</v>
       </c>
       <c r="C96">
-        <v>-35.69313855725006</v>
+        <v>-36.57206239912286</v>
       </c>
       <c r="D96">
-        <v>28.94574144274996</v>
+        <v>28.75633760087716</v>
       </c>
       <c r="E96">
-        <v>64.26288000000001</v>
+        <v>64.95240000000001</v>
       </c>
       <c r="F96">
-        <v>64.81488000000002</v>
+        <v>65.50440000000002</v>
       </c>
       <c r="G96">
         <v>0.176</v>
@@ -9159,37 +9159,37 @@
         <v>2.1</v>
       </c>
       <c r="M96">
-        <v>15.28334870400001</v>
+        <v>15.44593752</v>
       </c>
       <c r="N96">
-        <v>-13.18334870400001</v>
+        <v>-13.34593752</v>
       </c>
       <c r="O96">
-        <v>-3.295837176000001</v>
+        <v>-3.336484380000001</v>
       </c>
       <c r="P96">
-        <v>-9.887511528000005</v>
+        <v>-10.00945314</v>
       </c>
       <c r="Q96">
-        <v>-10.35751152800001</v>
+        <v>-10.47945314</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.003841475894631</v>
+        <v>2.395449771073558</v>
       </c>
       <c r="T96">
-        <v>18.9357575685301</v>
+        <v>22.72290908223613</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03435111049076538</v>
+        <v>0.03398951985402048</v>
       </c>
       <c r="W96">
-        <v>0.2277000081462776</v>
+        <v>0.227785271218422</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1374044419630615</v>
+        <v>0.1359580794160818</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3361684962111787</v>
+        <v>0.3380684962111786</v>
       </c>
       <c r="C97">
-        <v>-36.57206239912286</v>
+        <v>-37.44852366083924</v>
       </c>
       <c r="D97">
-        <v>28.75633760087716</v>
+        <v>28.56939633916078</v>
       </c>
       <c r="E97">
-        <v>64.95240000000001</v>
+        <v>65.64192000000001</v>
       </c>
       <c r="F97">
-        <v>65.50440000000002</v>
+        <v>66.19392000000002</v>
       </c>
       <c r="G97">
         <v>0.176</v>
@@ -9241,37 +9241,37 @@
         <v>2.1</v>
       </c>
       <c r="M97">
-        <v>15.44593752</v>
+        <v>15.60852633600001</v>
       </c>
       <c r="N97">
-        <v>-13.34593752</v>
+        <v>-13.50852633600001</v>
       </c>
       <c r="O97">
-        <v>-3.336484380000001</v>
+        <v>-3.377131584000002</v>
       </c>
       <c r="P97">
-        <v>-10.00945314</v>
+        <v>-10.13139475200001</v>
       </c>
       <c r="Q97">
-        <v>-10.47945314</v>
+        <v>-10.60139475200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.395449771073558</v>
+        <v>2.982862213841949</v>
       </c>
       <c r="T97">
-        <v>22.72290908223613</v>
+        <v>28.40363635279517</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03398951985402048</v>
+        <v>0.03363546235554109</v>
       </c>
       <c r="W97">
-        <v>0.227785271218422</v>
+        <v>0.2278687579765634</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1359580794160818</v>
+        <v>0.1345418494221644</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3380684962111786</v>
+        <v>0.3399684962111786</v>
       </c>
       <c r="C98">
-        <v>-37.44852366083923</v>
+        <v>-38.32257005895304</v>
       </c>
       <c r="D98">
-        <v>28.56939633916078</v>
+        <v>28.38486994104697</v>
       </c>
       <c r="E98">
-        <v>65.64192</v>
+        <v>66.33144</v>
       </c>
       <c r="F98">
-        <v>66.19392000000001</v>
+        <v>66.88344000000001</v>
       </c>
       <c r="G98">
         <v>0.176</v>
@@ -9323,37 +9323,37 @@
         <v>2.1</v>
       </c>
       <c r="M98">
-        <v>15.608526336</v>
+        <v>15.771115152</v>
       </c>
       <c r="N98">
-        <v>-13.508526336</v>
+        <v>-13.671115152</v>
       </c>
       <c r="O98">
-        <v>-3.377131584000001</v>
+        <v>-3.417778788000001</v>
       </c>
       <c r="P98">
-        <v>-10.131394752</v>
+        <v>-10.253336364</v>
       </c>
       <c r="Q98">
-        <v>-10.601394752</v>
+        <v>-10.723336364</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.982862213841941</v>
+        <v>3.961882951789255</v>
       </c>
       <c r="T98">
-        <v>28.4036363527951</v>
+        <v>37.87151513706014</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03363546235554111</v>
+        <v>0.03328870501166955</v>
       </c>
       <c r="W98">
-        <v>0.2278687579765634</v>
+        <v>0.2279505233582483</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1345418494221644</v>
+        <v>0.1331548200466781</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3399684962111786</v>
+        <v>0.3418684962111786</v>
       </c>
       <c r="C99">
-        <v>-38.32257005895304</v>
+        <v>-39.19424808514682</v>
       </c>
       <c r="D99">
-        <v>28.38486994104697</v>
+        <v>28.20271191485319</v>
       </c>
       <c r="E99">
-        <v>66.33144</v>
+        <v>67.02096</v>
       </c>
       <c r="F99">
-        <v>66.88344000000001</v>
+        <v>67.57296000000001</v>
       </c>
       <c r="G99">
         <v>0.176</v>
@@ -9405,37 +9405,37 @@
         <v>2.1</v>
       </c>
       <c r="M99">
-        <v>15.771115152</v>
+        <v>15.933703968</v>
       </c>
       <c r="N99">
-        <v>-13.671115152</v>
+        <v>-13.833703968</v>
       </c>
       <c r="O99">
-        <v>-3.417778788000001</v>
+        <v>-3.458425992000001</v>
       </c>
       <c r="P99">
-        <v>-10.253336364</v>
+        <v>-10.375277976</v>
       </c>
       <c r="Q99">
-        <v>-10.723336364</v>
+        <v>-10.845277976</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.961882951789255</v>
+        <v>5.919924427683882</v>
       </c>
       <c r="T99">
-        <v>37.87151513706014</v>
+        <v>56.80727270559019</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03328870501166955</v>
+        <v>0.03294902434828516</v>
       </c>
       <c r="W99">
-        <v>0.2279505233582483</v>
+        <v>0.2280306200586744</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1331548200466781</v>
+        <v>0.1317960973931406</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3418684962111786</v>
+        <v>0.3437684962111786</v>
       </c>
       <c r="C100">
-        <v>-39.19424808514682</v>
+        <v>-40.06360304528383</v>
       </c>
       <c r="D100">
-        <v>28.20271191485319</v>
+        <v>28.02287695471619</v>
       </c>
       <c r="E100">
-        <v>67.02096</v>
+        <v>67.71048</v>
       </c>
       <c r="F100">
-        <v>67.57296000000001</v>
+        <v>68.26248000000001</v>
       </c>
       <c r="G100">
         <v>0.176</v>
@@ -9487,37 +9487,37 @@
         <v>2.1</v>
       </c>
       <c r="M100">
-        <v>15.933703968</v>
+        <v>16.096292784</v>
       </c>
       <c r="N100">
-        <v>-13.833703968</v>
+        <v>-13.996292784</v>
       </c>
       <c r="O100">
-        <v>-3.458425992000001</v>
+        <v>-3.499073196000001</v>
       </c>
       <c r="P100">
-        <v>-10.375277976</v>
+        <v>-10.497219588</v>
       </c>
       <c r="Q100">
-        <v>-10.845277976</v>
+        <v>-10.967219588</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.919924427683882</v>
+        <v>11.79404885536776</v>
       </c>
       <c r="T100">
-        <v>56.80727270559019</v>
+        <v>113.6145454111804</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03294902434828516</v>
+        <v>0.03261620592052471</v>
       </c>
       <c r="W100">
-        <v>0.2280306200586744</v>
+        <v>0.2281090986439403</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1317960973931406</v>
+        <v>0.1304648236820988</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3437684962111786</v>
-      </c>
-      <c r="C101">
-        <v>-40.06360304528383</v>
-      </c>
-      <c r="D101">
-        <v>28.02287695471619</v>
-      </c>
-      <c r="E101">
-        <v>67.71048</v>
-      </c>
-      <c r="F101">
-        <v>68.26248000000001</v>
-      </c>
-      <c r="G101">
-        <v>0.176</v>
-      </c>
-      <c r="H101">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.63</v>
-      </c>
-      <c r="K101">
-        <v>-0.4700000000000002</v>
-      </c>
-      <c r="L101">
-        <v>2.1</v>
-      </c>
-      <c r="M101">
-        <v>16.096292784</v>
-      </c>
-      <c r="N101">
-        <v>-13.996292784</v>
-      </c>
-      <c r="O101">
-        <v>-3.499073196000001</v>
-      </c>
-      <c r="P101">
-        <v>-10.497219588</v>
-      </c>
-      <c r="Q101">
-        <v>-10.967219588</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.79404885536776</v>
-      </c>
-      <c r="T101">
-        <v>113.6145454111804</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03261620592052471</v>
-      </c>
-      <c r="W101">
-        <v>0.2281090986439403</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1304648236820988</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
